--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570DA53D-11EA-4F43-9773-E4B869A7198E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4B1206-8151-4EB0-B143-1801576A5C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3258,10 +3258,10 @@
     <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
+    <t>中國旺旺</t>
+  </si>
+  <si>
     <t>0151.HK</t>
-  </si>
-  <si>
-    <t>中國旺旺</t>
   </si>
 </sst>
 </file>
@@ -5359,7 +5359,7 @@
         <v>532</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E4" s="430" t="s">
         <v>536</v>
@@ -5373,7 +5373,7 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E5" s="433" t="s">
         <v>538</v>
@@ -16328,7 +16328,7 @@
         <v>399</v>
       </c>
       <c r="F14" s="309" t="str">
-        <f>IF(ROUND(F17,2)=ROUND(C17,2),"I","II")</f>
+        <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
@@ -16366,14 +16366,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E16" s="308" t="s">
         <v>400</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="D21" s="299">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="D22" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="D23" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="D24" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
@@ -16690,7 +16690,7 @@
       </c>
       <c r="D25" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="D26" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="D27" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="D28" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="D29" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="D30" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
@@ -17090,7 +17090,7 @@
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
@@ -19847,7 +19847,7 @@
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -19887,7 +19887,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>3.4071209167200467E-2</v>
+        <v>3.4071209167200502E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4B1206-8151-4EB0-B143-1801576A5C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154BCE09-483B-4132-9F42-407A6DBE8F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.6900000000000004</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55356.403623149999</v>
+        <v>54412.157932350005</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15262981708994752</v>
+        <v>0.15945256419696016</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5561,7 +5561,7 @@
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,7 +5576,7 @@
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6142428861876476E-2</v>
+        <v>6.729023673800448E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.4533622559652928E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.29131237091673107</v>
+        <v>0.29131237091673101</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.3349574284052374</v>
+        <v>0.33495742840523723</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.4533622559652928E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.4533622559652928E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4861407249466941E-2</v>
+        <v>5.5813449023861164E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6142428861876476E-2</v>
+        <v>6.729023673800448E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4623043544565995E-2</v>
+        <v>6.5744484647291643E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0309155545637955E-2</v>
+        <v>6.1355735251419088E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8191766746022143E-2</v>
+        <v>7.9548673761137487E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1955162172678389E-2</v>
+        <v>7.3203841776542655E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.6900000000000004</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15262981708994752</v>
+        <v>0.15945256419696016</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20041,7 +20041,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.29131237091673107</v>
+        <v>0.29131237091673101</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20053,7 +20053,7 @@
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.3349574284052374</v>
+        <v>0.33495742840523723</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.6900000000000004</v>
+        <v>4.6100000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55356.403623149999</v>
+        <v>54412.157932350005</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15262981708994752</v>
+        <v>0.15945256419696016</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6142428861876476E-2</v>
+        <v>6.729023673800448E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.4533622559652928E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.29131237091673107</v>
+        <v>0.29131237091673101</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.3349574284052374</v>
+        <v>0.33495742840523723</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154BCE09-483B-4132-9F42-407A6DBE8F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A998DB-0F55-4D56-BE3E-9FD9D5F8EC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.6100000000000003</v>
+        <v>4.63</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>54412.157932350005</v>
+        <v>54648.219355049994</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15945256419696016</v>
+        <v>0.15773186966665081</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.729023673800448E-2</v>
+        <v>6.6999566168941843E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4533622559652928E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4533622559652928E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4533622559652928E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5813449023861164E-2</v>
+        <v>5.5572354211663059E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.729023673800448E-2</v>
+        <v>6.6999566168941843E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5744484647291643E-2</v>
+        <v>6.5460491193091691E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.1355735251419088E-2</v>
+        <v>6.1090699677978838E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9548673761137487E-2</v>
+        <v>7.9205050980311859E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3203841776542655E-2</v>
+        <v>7.2887626477291939E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.6100000000000003</v>
+        <v>4.63</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15945256419696016</v>
+        <v>0.15773186966665081</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.6100000000000003</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>54412.157932350005</v>
+        <v>54648.219355049994</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15945256419696016</v>
+        <v>0.15773186966665081</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.729023673800448E-2</v>
+        <v>6.6999566168941843E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4533622559652928E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A998DB-0F55-4D56-BE3E-9FD9D5F8EC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3789AE3C-998B-446A-85FD-A6D91FD1A09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>54648.219355049994</v>
+        <v>55238.372911799997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15773186966665081</v>
+        <v>0.15347397994697132</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6999566168941843E-2</v>
+        <v>6.6283758838077078E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4017094017094018E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4017094017094018E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4017094017094018E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5572354211663059E-2</v>
+        <v>5.4978632478632473E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6999566168941843E-2</v>
+        <v>6.6283758838077078E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5460491193091691E-2</v>
+        <v>6.4761126970943272E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.1090699677978838E-2</v>
+        <v>6.0438021262615819E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9205050980311859E-2</v>
+        <v>7.8358843170693138E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2887626477291939E-2</v>
+        <v>7.2108912519201221E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15773186966665081</v>
+        <v>0.15347397994697132</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>54648.219355049994</v>
+        <v>55238.372911799997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15773186966665081</v>
+        <v>0.15347397994697132</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6999566168941843E-2</v>
+        <v>6.6283758838077078E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4017094017094018E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3789AE3C-998B-446A-85FD-A6D91FD1A09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4C1F5C-9926-429F-8193-1E22A4CA1A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.68</v>
+        <v>4.82</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55238.372911799997</v>
+        <v>56890.802870700005</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15347397994697132</v>
+        <v>0.14187358415295637</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6283758838077078E-2</v>
+        <v>6.4358504431991842E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4017094017094018E-2</v>
+        <v>3.3029045643153523E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4017094017094018E-2</v>
+        <v>3.3029045643153523E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4017094017094018E-2</v>
+        <v>3.3029045643153523E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4978632478632473E-2</v>
+        <v>5.33817427385892E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6283758838077078E-2</v>
+        <v>6.4358504431991842E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4761126970943272E-2</v>
+        <v>6.2880098386724995E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0438021262615819E-2</v>
+        <v>5.8682560064116603E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8358843170693138E-2</v>
+        <v>7.6082860174033984E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2108912519201221E-2</v>
+        <v>7.0014462777979597E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.68</v>
+        <v>4.82</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15347397994697132</v>
+        <v>0.14187358415295637</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.68</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55238.372911799997</v>
+        <v>56890.802870700005</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15347397994697132</v>
+        <v>0.14187358415295637</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6283758838077078E-2</v>
+        <v>6.4358504431991842E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4017094017094018E-2</v>
+        <v>3.3029045643153523E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4C1F5C-9926-429F-8193-1E22A4CA1A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE7C80B-BCD9-4496-B9F8-C96608233A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.82</v>
+        <v>4.99</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>56890.802870700005</v>
+        <v>58897.324963650004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14187358415295637</v>
+        <v>0.12838808407975857</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4358504431991842E-2</v>
+        <v>6.2165930132705549E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3029045643153523E-2</v>
+        <v>3.1903807615230463E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3029045643153523E-2</v>
+        <v>3.1903807615230463E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3029045643153523E-2</v>
+        <v>3.1903807615230463E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.33817427385892E-2</v>
+        <v>5.1563126252505004E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4358504431991842E-2</v>
+        <v>6.2165930132705549E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.2880098386724995E-2</v>
+        <v>6.0737890626055009E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.8682560064116603E-2</v>
+        <v>5.6683354611030461E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6082860174033984E-2</v>
+        <v>7.3490858925620017E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0014462777979597E-2</v>
+        <v>6.7629200519010349E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.82</v>
+        <v>4.99</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14187358415295637</v>
+        <v>0.12838808407975857</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.82</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>56890.802870700005</v>
+        <v>58897.324963650004</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14187358415295637</v>
+        <v>0.12838808407975857</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4358504431991842E-2</v>
+        <v>6.2165930132705549E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3029045643153523E-2</v>
+        <v>3.1903807615230463E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE7C80B-BCD9-4496-B9F8-C96608233A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5128CA-B4E9-448A-9494-967B316E2D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>58897.324963650004</v>
+        <v>58543.232829599998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12838808407975857</v>
+        <v>0.13072214847287472</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.2165930132705549E-2</v>
+        <v>6.254193374237918E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.1903807615230463E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1903807615230463E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1903807615230463E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1563126252505004E-2</v>
+        <v>5.1874999999999998E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2165930132705549E-2</v>
+        <v>6.254193374237918E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.0737890626055009E-2</v>
+        <v>6.1105256900002923E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.6683354611030461E-2</v>
+        <v>5.7026197481661697E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3490858925620017E-2</v>
+        <v>7.3935360088476593E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7629200519010349E-2</v>
+        <v>6.8038248102794685E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12838808407975857</v>
+        <v>0.13072214847287472</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>58897.324963650004</v>
+        <v>58543.232829599998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12838808407975857</v>
+        <v>0.13072214847287472</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.2165930132705549E-2</v>
+        <v>6.254193374237918E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.1903807615230463E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5128CA-B4E9-448A-9494-967B316E2D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8F1A58-7815-4DCB-95B6-227E0F9EF67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.96</v>
+        <v>5.09</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>58543.232829599998</v>
+        <v>60077.632077150003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13072214847287472</v>
+        <v>0.12074345393324551</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.254193374237918E-2</v>
+        <v>6.0944595552495227E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.1277013752455798E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.1277013752455798E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.1277013752455798E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1874999999999998E-2</v>
+        <v>5.0550098231827108E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.254193374237918E-2</v>
+        <v>6.0944595552495227E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.1105256900002923E-2</v>
+        <v>5.9544611831829963E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7026197481661697E-2</v>
+        <v>5.5569732712974856E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3935360088476593E-2</v>
+        <v>7.2047030655961464E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8038248102794685E-2</v>
+        <v>6.6300532532389322E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.96</v>
+        <v>5.09</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13072214847287472</v>
+        <v>0.12074345393324551</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.96</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>58543.232829599998</v>
+        <v>60077.632077150003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.13072214847287472</v>
+        <v>0.12074345393324551</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.254193374237918E-2</v>
+        <v>6.0944595552495227E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.1277013752455798E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8F1A58-7815-4DCB-95B6-227E0F9EF67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C351A7-C9DE-42EB-85FB-38D72319F629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>5.09</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>60077.632077150003</v>
+        <v>58779.294252300002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12074345393324551</v>
+        <v>0.12916398328704107</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.0944595552495227E-2</v>
+        <v>6.2290761317710983E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.1277013752455798E-2</v>
+        <v>3.1967871485943773E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1277013752455798E-2</v>
+        <v>3.1967871485943773E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1277013752455798E-2</v>
+        <v>3.1967871485943773E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0550098231827108E-2</v>
+        <v>5.1666666666666659E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.0944595552495227E-2</v>
+        <v>6.2290761317710983E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>5.9544611831829963E-2</v>
+        <v>6.0859854261850296E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5569732712974856E-2</v>
+        <v>5.6797176608241365E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2047030655961464E-2</v>
+        <v>7.3638430931494747E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6300532532389322E-2</v>
+        <v>6.7765002126478235E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>5.09</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12074345393324551</v>
+        <v>0.12916398328704107</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>5.09</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>60077.632077150003</v>
+        <v>58779.294252300002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12074345393324551</v>
+        <v>0.12916398328704107</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.0944595552495227E-2</v>
+        <v>6.2290761317710983E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.1277013752455798E-2</v>
+        <v>3.1967871485943773E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C351A7-C9DE-42EB-85FB-38D72319F629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D267E441-A9D9-4908-837E-E38A15ED4417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.9800000000000004</v>
+        <v>4.96</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>58779.294252300002</v>
+        <v>58543.232829599998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12916398328704107</v>
+        <v>0.13072214847287472</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.2290761317710983E-2</v>
+        <v>6.254193374237918E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.1967871485943773E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1967871485943773E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1967871485943773E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1666666666666659E-2</v>
+        <v>5.1874999999999998E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2290761317710983E-2</v>
+        <v>6.254193374237918E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.0859854261850296E-2</v>
+        <v>6.1105256900002923E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.6797176608241365E-2</v>
+        <v>5.7026197481661697E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3638430931494747E-2</v>
+        <v>7.3935360088476593E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7765002126478235E-2</v>
+        <v>6.8038248102794685E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.9800000000000004</v>
+        <v>4.96</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12916398328704107</v>
+        <v>0.13072214847287472</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.9800000000000004</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>58779.294252300002</v>
+        <v>58543.232829599998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12916398328704107</v>
+        <v>0.13072214847287472</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.2290761317710983E-2</v>
+        <v>6.254193374237918E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.1967871485943773E-2</v>
+        <v>3.2096774193548387E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D267E441-A9D9-4908-837E-E38A15ED4417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FCA46D-ABE1-F242-BEBB-F9CC6B7DD51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3269,27 +3280,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4041,7 +4052,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4083,17 +4094,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4102,7 +4113,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4176,10 +4187,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4190,7 +4201,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4228,7 +4239,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4238,7 +4249,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4249,19 +4260,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4269,8 +4280,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4293,29 +4304,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4332,15 +4343,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4351,11 +4362,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4416,14 +4427,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4436,7 +4447,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4473,7 +4484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4490,7 +4501,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4536,7 +4547,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4551,13 +4562,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4573,53 +4584,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4636,7 +4647,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4649,21 +4660,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4673,14 +4684,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4689,8 +4700,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4702,7 +4713,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4710,7 +4721,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4749,7 +4760,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4763,39 +4774,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4806,7 +4817,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4817,10 +4828,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4829,7 +4840,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4842,7 +4853,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4851,8 +4862,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4860,10 +4871,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4872,10 +4883,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4892,16 +4903,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4922,7 +4933,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4940,7 +4951,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4950,10 +4961,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4968,7 +4979,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4982,34 +4993,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5030,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,21 +5048,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5324,7 +5335,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5333,7 +5344,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5346,7 +5357,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>537</v>
       </c>
@@ -5354,7 +5365,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>532</v>
       </c>
@@ -5368,7 +5379,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5382,7 +5393,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5392,7 +5403,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5402,16 +5413,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5419,43 +5430,43 @@
         <v>11803071135</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>58543.232829599998</v>
+        <v>58425.202118250003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13072214847287472</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.13150443474697285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5470,7 +5481,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5484,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>531</v>
       </c>
@@ -5498,7 +5509,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -5514,7 +5525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5530,11 +5541,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5549,7 +5560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
@@ -5579,7 +5590,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
@@ -5594,7 +5605,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
@@ -5609,11 +5620,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5623,25 +5634,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5650,16 +5661,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5672,20 +5683,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5698,7 +5709,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5711,16 +5722,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5733,16 +5744,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5757,7 +5768,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5772,7 +5783,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5785,12 +5796,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5803,16 +5814,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5825,8 +5836,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5834,7 +5845,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5847,25 +5858,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5878,7 +5889,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5891,23 +5902,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.254193374237918E-2</v>
+        <v>6.2668281083272867E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.2161616161616162E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5917,7 +5928,7 @@
         <v>0.5132040580286571</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5928,7 +5939,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5941,7 +5952,7 @@
         <v>0.28020929484316204</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5955,7 +5966,7 @@
         <v>0.21248573712552665</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5969,7 +5980,7 @@
         <v>0.86056930273853416</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5983,7 +5994,7 @@
         <v>1.532381509863507</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -5993,45 +6004,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6045,7 +6056,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6059,7 +6070,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6069,7 +6080,7 @@
         <v>0.27351475277205878</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6079,16 +6090,16 @@
         <v>0.94608729427783522</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6102,7 +6113,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6116,7 +6127,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6130,16 +6141,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6153,7 +6164,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6167,10 +6178,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
@@ -6184,7 +6195,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6194,42 +6205,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6238,7 +6249,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6247,7 +6258,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6256,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6265,36 +6276,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
@@ -6307,7 +6318,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
@@ -6320,21 +6331,21 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6351,7 +6362,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (15yrs)</v>
@@ -6373,7 +6384,7 @@
         <v>-5.8810474812513162E-2</v>
       </c>
     </row>
-    <row r="119" spans="2:6">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (15yrs)</v>
@@ -6395,7 +6406,7 @@
         <v>-2.726690194899704E-2</v>
       </c>
     </row>
-    <row r="120" spans="2:6">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (15yrs)</v>
@@ -6417,7 +6428,7 @@
         <v>3.7139913387016728E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (15yrs)</v>
@@ -6439,7 +6450,7 @@
         <v>0.10276836564090074</v>
       </c>
     </row>
-    <row r="122" spans="2:6">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (15yrs)</v>
@@ -6461,16 +6472,16 @@
         <v>0.13581567914138118</v>
       </c>
     </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6483,7 +6494,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6492,7 +6503,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6502,30 +6513,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6534,7 +6545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6547,14 +6558,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6573,7 +6584,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6594,7 +6605,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6615,14 +6626,14 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6641,7 +6652,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6662,7 +6673,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6683,7 +6694,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6693,21 +6704,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6716,80 +6727,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6829,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6845,15 +6856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>HKD</v>
@@ -6902,7 +6913,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6918,7 +6929,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6926,7 +6937,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6946,7 +6957,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6966,7 +6977,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -6988,7 +6999,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7008,7 +7019,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7024,7 +7035,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7040,7 +7051,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7060,7 +7071,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7076,7 +7087,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7096,7 +7107,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7116,7 +7127,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7136,7 +7147,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7156,7 +7167,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7176,13 +7187,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7204,7 +7215,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7224,7 +7235,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7240,7 +7251,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7260,7 +7271,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7280,7 +7291,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7300,7 +7311,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7328,7 +7339,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7336,7 +7347,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7358,7 +7369,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7379,7 +7390,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7400,7 +7411,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7421,7 +7432,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7442,7 +7453,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7458,12 +7469,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7512,7 +7523,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7561,7 +7572,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7610,7 +7621,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7659,7 +7670,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7708,7 +7719,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7757,7 +7768,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7806,7 +7817,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7855,7 +7866,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7904,7 +7915,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7953,7 +7964,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8002,7 +8013,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8051,7 +8062,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8100,12 +8111,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8154,7 +8165,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8203,12 +8214,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8257,7 +8268,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8306,7 +8317,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8355,7 +8366,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8404,13 +8415,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8459,7 +8470,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8508,7 +8519,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8557,7 +8568,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8606,7 +8617,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8655,12 +8666,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8710,7 +8721,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8759,14 +8770,14 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
       <c r="C70" s="98">
         <f>IF(D$36="","",C43/D43-1)</f>
-        <v>4.6210734019126232E-2</v>
+        <v>4.621073401912601E-2</v>
       </c>
       <c r="D70" s="98" t="str">
         <f t="shared" ref="D70:M70" si="36">IF(E$36="","",D43/E43-1)</f>
@@ -8809,7 +8820,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8858,7 +8869,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8908,7 +8919,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8924,13 +8935,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8979,7 +8990,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9013,7 +9024,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9047,7 +9058,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9096,7 +9107,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9177,7 +9188,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9188,7 +9199,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9204,7 +9215,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9215,7 +9226,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9235,7 +9246,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9256,7 +9267,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9277,7 +9288,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9298,7 +9309,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9319,7 +9330,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9340,7 +9351,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9361,7 +9372,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9381,7 +9392,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9393,7 +9404,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9417,12 +9428,12 @@
         <v>10301292</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9442,7 +9453,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9462,7 +9473,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9482,7 +9493,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9502,7 +9513,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9522,7 +9533,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9543,7 +9554,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9563,7 +9574,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9583,7 +9594,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9595,7 +9606,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9607,7 +9618,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9631,7 +9642,7 @@
         <v>3019689</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9648,7 +9659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9667,7 +9678,7 @@
         <v>7044710.8499999996</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9682,7 +9693,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9701,7 +9712,7 @@
         <v>7052296.8499999996</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9717,7 +9728,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9734,7 +9745,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9754,7 +9765,7 @@
         <v>16536245.85</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9765,7 +9776,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9778,7 +9789,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9797,7 +9808,7 @@
         <v>3215264.85</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9813,7 +9824,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9829,7 +9840,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9845,7 +9856,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9864,7 +9875,7 @@
         <v>641518.70000000007</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9884,7 +9895,7 @@
         <v>13320981</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9904,7 +9915,7 @@
         <v>13134092</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9923,7 +9934,7 @@
         <v>186889</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9934,7 +9945,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9948,7 +9959,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9962,7 +9973,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9977,10 +9988,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9993,7 +10004,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10007,7 +10018,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10018,10 +10029,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10033,7 +10044,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10047,7 +10058,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10061,10 +10072,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10076,7 +10087,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10087,7 +10098,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10098,10 +10109,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10113,7 +10124,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10129,7 +10140,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10140,7 +10151,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10154,7 +10165,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10170,7 +10181,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10180,7 +10191,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10190,7 +10201,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10200,7 +10211,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10210,10 +10221,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10225,7 +10236,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10241,7 +10252,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10257,7 +10268,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10270,7 +10281,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10283,10 +10294,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10298,7 +10309,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10312,7 +10323,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10326,7 +10337,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10340,7 +10351,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10354,7 +10365,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10365,7 +10376,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10373,7 +10384,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10390,7 +10401,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10407,7 +10418,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10424,7 +10435,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10460,19 +10471,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10529,7 +10540,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10552,7 +10563,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10572,7 +10583,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10629,7 +10640,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10684,7 +10695,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10739,7 +10750,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10794,7 +10805,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10851,7 +10862,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10908,7 +10919,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10963,7 +10974,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11018,7 +11029,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11073,7 +11084,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11130,7 +11141,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11187,7 +11198,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11242,7 +11253,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11297,7 +11308,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11323,7 +11334,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11348,7 +11359,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11405,7 +11416,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11424,7 +11435,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11447,7 +11458,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11468,7 +11479,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11525,7 +11536,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11582,7 +11593,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11639,7 +11650,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11696,18 +11707,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11764,7 +11775,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11822,7 +11833,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11879,7 +11890,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11934,18 +11945,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12002,18 +12013,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12068,18 +12079,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12137,10 +12148,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12163,14 +12174,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12225,7 +12236,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12280,7 +12291,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12337,7 +12348,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12392,11 +12403,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12406,7 +12417,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12430,7 +12441,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12454,7 +12465,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12509,11 +12520,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12523,7 +12534,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12578,7 +12589,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12633,7 +12644,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12688,7 +12699,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12743,7 +12754,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12799,7 +12810,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12854,11 +12865,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12868,7 +12879,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12893,7 +12904,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12918,7 +12929,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12943,7 +12954,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12970,10 +12981,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12996,7 +13007,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13017,7 +13028,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13074,7 +13085,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13131,7 +13142,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13188,7 +13199,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13245,7 +13256,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13302,7 +13313,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13359,7 +13370,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13416,7 +13427,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13473,7 +13484,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13531,7 +13542,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13588,7 +13599,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13645,7 +13656,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13704,7 +13715,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13730,7 +13741,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13754,7 +13765,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13811,18 +13822,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13878,7 +13889,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13934,7 +13945,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13989,7 +14000,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14010,23 +14021,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.2161616161616162E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.2161616161616162E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1874999999999998E-2</v>
+        <v>5.1979797979797973E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14065,11 +14076,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14090,7 +14101,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14147,7 +14158,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14204,10 +14215,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14230,7 +14241,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14240,7 +14251,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14297,7 +14308,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14354,7 +14365,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14411,7 +14422,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14468,7 +14479,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14525,11 +14536,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14552,7 +14563,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14609,7 +14620,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14666,7 +14677,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14693,18 +14704,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14758,7 +14769,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14813,11 +14824,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14876,7 +14887,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14934,7 +14945,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14991,7 +15002,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15050,7 +15061,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15110,7 +15121,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15129,7 +15140,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15152,7 +15163,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15173,7 +15184,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15231,25 +15242,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.254193374237918E-2</v>
+        <v>6.2668281083272867E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.1105256900002923E-2</v>
+        <v>6.122870186343727E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7026197481661697E-2</v>
+        <v>5.7141401921018589E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15288,18 +15299,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3935360088476593E-2</v>
+        <v>7.4084724452291695E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8038248102794685E-2</v>
+        <v>6.8175699109062959E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15338,688 +15349,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16041,16 +16052,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16065,7 +16076,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16080,7 +16091,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16112,7 +16123,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16140,7 +16151,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16173,7 +16184,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16203,7 +16214,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16238,7 +16249,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*HKD</v>
@@ -16264,7 +16275,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
@@ -16286,7 +16297,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
@@ -16302,7 +16313,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16317,7 +16328,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16335,7 +16346,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16360,7 +16371,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16376,7 +16387,7 @@
         <v>3.4071209167200502E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>549</v>
       </c>
@@ -16395,7 +16406,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16422,10 +16433,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16464,7 +16475,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16513,7 +16524,7 @@
         <v>3530214.9669478289</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16562,7 +16573,7 @@
         <v>3403723.6918339306</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16619,7 +16630,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16676,7 +16687,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16733,7 +16744,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16782,7 +16793,7 @@
         <v>2941486.6418798994</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16831,7 +16842,7 @@
         <v>2836090.1151682204</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16880,7 +16891,7 @@
         <v>2734470.0556635396</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16929,7 +16940,7 @@
         <v>2636491.148616781</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16978,7 +16989,7 @@
         <v>2542022.9277471104</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17027,7 +17038,7 @@
         <v>2450939.6015162719</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17076,7 +17087,7 @@
         <v>2363119.8856276996</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17133,7 +17144,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17190,7 +17201,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17247,7 +17258,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17296,7 +17307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17345,7 +17356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17394,7 +17405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17443,7 +17454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17492,7 +17503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17541,7 +17552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17590,7 +17601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17639,7 +17650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17688,7 +17699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17737,7 +17748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17786,7 +17797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17843,7 +17854,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17900,7 +17911,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17957,7 +17968,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18014,7 +18025,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18060,7 +18071,7 @@
         <v>29799388.838375315</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18073,10 +18084,10 @@
         <v>71328036.646042943</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18091,7 +18102,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>71328036.646042943</v>
@@ -18123,7 +18134,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18150,7 +18161,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18176,7 +18187,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18202,7 +18213,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18228,7 +18239,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18254,7 +18265,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18280,7 +18291,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18306,7 +18317,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18332,7 +18343,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18358,7 +18369,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18384,7 +18395,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18419,7 +18430,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18454,7 +18465,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18489,7 +18500,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18524,7 +18535,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18545,7 +18556,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18569,7 +18580,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18597,7 +18608,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18628,7 +18639,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18659,7 +18670,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18690,7 +18701,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18721,7 +18732,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18752,7 +18763,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -18783,7 +18794,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -18814,7 +18825,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -18846,7 +18857,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -18877,7 +18888,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -18909,7 +18920,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -18941,7 +18952,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -18973,7 +18984,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -19005,7 +19016,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19037,7 +19048,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19069,7 +19080,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19092,7 +19103,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19120,7 +19131,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19148,7 +19159,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19176,7 +19187,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19204,7 +19215,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19232,7 +19243,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19245,16 +19256,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19266,7 +19277,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19278,7 +19289,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19290,7 +19301,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19302,7 +19313,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19342,14 +19353,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19359,7 +19370,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19368,7 +19379,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19389,14 +19400,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19409,7 +19420,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19422,7 +19433,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19435,7 +19446,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19448,14 +19459,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19465,7 +19476,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19478,7 +19489,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19491,7 +19502,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19504,7 +19515,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19514,7 +19525,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19522,7 +19533,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19534,18 +19545,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19566,7 +19577,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19590,7 +19601,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19613,7 +19624,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19636,7 +19647,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
@@ -19650,12 +19661,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19676,7 +19687,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19699,7 +19710,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19722,16 +19733,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19751,13 +19762,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,10 +19779,10 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13072214847287472</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>0.13150443474697285</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
@@ -19791,7 +19802,7 @@
         <v>2.4767426927084515E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
@@ -19810,7 +19821,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19820,7 +19831,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19829,7 +19840,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>550</v>
       </c>
@@ -19841,7 +19852,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19851,7 +19862,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19861,7 +19872,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19869,7 +19880,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19882,7 +19893,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19894,7 +19905,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -19910,7 +19921,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19922,7 +19933,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19932,7 +19943,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19944,7 +19955,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19954,7 +19965,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19970,7 +19981,7 @@
         <v>8.8521421695043054E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="13.9">
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19980,12 +19991,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19995,7 +20006,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20008,13 +20019,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20035,7 +20046,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20060,7 +20071,7 @@
         <v>0.49521704363132646</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="13.15">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20085,7 +20096,7 @@
         <v>0.37184400405652518</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="13.15">
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20106,7 +20117,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20131,7 +20142,7 @@
         <v>0.22528831503764324</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="13.15">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20172,7 +20183,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20181,7 +20192,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20195,7 +20206,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>541</v>
       </c>
@@ -20204,7 +20215,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>533</v>
       </c>
@@ -20221,7 +20232,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20237,7 +20248,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20247,7 +20258,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20258,16 +20269,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20276,43 +20287,43 @@
         <v>11803071135</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>58543.232829599998</v>
+        <v>58425.202118250003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.13072214847287472</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.13150443474697285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20328,7 +20339,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20344,7 +20355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>534</v>
       </c>
@@ -20360,7 +20371,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
@@ -20377,7 +20388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20393,11 +20404,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20413,7 +20424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
@@ -20429,7 +20440,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
@@ -20445,7 +20456,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
@@ -20461,7 +20472,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
@@ -20477,7 +20488,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20487,25 +20498,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20514,7 +20525,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>500</v>
       </c>
@@ -20523,7 +20534,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20536,11 +20547,11 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>501</v>
       </c>
@@ -20549,7 +20560,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20562,7 +20573,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20575,7 +20586,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>502</v>
       </c>
@@ -20584,7 +20595,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20597,7 +20608,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>503</v>
       </c>
@@ -20606,7 +20617,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20621,7 +20632,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20636,7 +20647,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20649,12 +20660,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20667,7 +20678,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>505</v>
       </c>
@@ -20676,7 +20687,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20689,16 +20700,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20711,25 +20722,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20742,7 +20753,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20755,23 +20766,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.254193374237918E-2</v>
+        <v>6.2668281083272867E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2096774193548387E-2</v>
+        <v>3.2161616161616162E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20781,7 +20792,7 @@
         <v>0.5132040580286571</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20792,7 +20803,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20805,7 +20816,7 @@
         <v>0.28020929484316204</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20819,7 +20830,7 @@
         <v>0.21248573712552665</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20833,7 +20844,7 @@
         <v>0.86056930273853416</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20847,7 +20858,7 @@
         <v>1.532381509863507</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20857,43 +20868,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20906,7 +20917,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -20919,7 +20930,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20928,7 +20939,7 @@
         <v>0.27351475277205878</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20937,12 +20948,12 @@
         <v>0.94608729427783522</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20955,7 +20966,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -20968,7 +20979,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -20981,12 +20992,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -20999,7 +21010,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21012,7 +21023,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
@@ -21025,7 +21036,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21035,49 +21046,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21087,7 +21098,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21097,7 +21108,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21107,7 +21118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>534</v>
@@ -21116,47 +21127,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
@@ -21170,7 +21181,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
@@ -21184,29 +21195,29 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21224,7 +21235,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21247,7 +21258,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21270,7 +21281,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21292,7 +21303,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21314,7 +21325,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21336,7 +21347,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>518</v>
       </c>
@@ -21345,7 +21356,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21358,16 +21369,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21377,30 +21388,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21409,7 +21420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21422,14 +21433,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21448,7 +21459,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21469,7 +21480,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21490,7 +21501,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21509,7 +21520,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21530,7 +21541,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21551,7 +21562,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21561,50 +21572,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21613,57 +21624,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21692,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FCA46D-ABE1-F242-BEBB-F9CC6B7DD51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D01B309-324E-45C5-9A3E-4329EE14C115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3280,27 +3269,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4052,7 +4041,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4094,17 +4083,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4113,7 +4102,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4187,10 +4176,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4201,7 +4190,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4239,7 +4228,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4249,7 +4238,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4260,19 +4249,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4280,8 +4269,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4304,29 +4293,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4343,15 +4332,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4362,11 +4351,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4427,14 +4416,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4447,7 +4436,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4484,7 +4473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4501,7 +4490,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4547,7 +4536,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4562,13 +4551,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4584,53 +4573,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4647,7 +4636,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4660,21 +4649,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4684,14 +4673,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4700,8 +4689,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4713,7 +4702,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4721,7 +4710,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4760,7 +4749,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4774,39 +4763,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4817,7 +4806,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4828,10 +4817,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4840,7 +4829,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4853,7 +4842,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4862,8 +4851,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4871,10 +4860,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4883,10 +4872,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4903,16 +4892,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4933,7 +4922,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4951,7 +4940,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4961,10 +4950,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4979,7 +4968,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4993,34 +4982,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,30 +5019,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5335,7 +5324,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5344,7 +5333,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5357,7 +5346,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>537</v>
       </c>
@@ -5365,7 +5354,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>532</v>
       </c>
@@ -5379,7 +5368,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5393,7 +5382,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5403,7 +5392,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5413,16 +5402,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.95</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5430,43 +5419,43 @@
         <v>11803071135</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>58425.202118250003</v>
+        <v>57835.048561500007</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13150443474697285</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.13544831512510774</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5481,7 +5470,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5495,7 +5484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>531</v>
       </c>
@@ -5509,7 +5498,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -5525,7 +5514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5541,11 +5530,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5560,7 +5549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
@@ -5590,7 +5579,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
@@ -5605,7 +5594,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
@@ -5620,11 +5609,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5634,25 +5623,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5661,16 +5650,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5683,20 +5672,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5709,7 +5698,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5722,16 +5711,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5744,16 +5733,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5768,7 +5757,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5783,7 +5772,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5796,12 +5785,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5814,16 +5803,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5836,8 +5825,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5845,7 +5834,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5858,25 +5847,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5889,7 +5878,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5902,23 +5891,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.2668281083272867E-2</v>
+        <v>6.3307753339224629E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2161616161616162E-2</v>
+        <v>3.2489795918367349E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5928,7 +5917,7 @@
         <v>0.5132040580286571</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5939,7 +5928,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5952,7 +5941,7 @@
         <v>0.28020929484316204</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5966,7 +5955,7 @@
         <v>0.21248573712552665</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5980,7 +5969,7 @@
         <v>0.86056930273853416</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5994,7 +5983,7 @@
         <v>1.532381509863507</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6004,45 +5993,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6056,7 +6045,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6070,7 +6059,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6080,7 +6069,7 @@
         <v>0.27351475277205878</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6090,16 +6079,16 @@
         <v>0.94608729427783522</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6113,7 +6102,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6127,7 +6116,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6141,16 +6130,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6164,7 +6153,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6178,10 +6167,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
@@ -6195,7 +6184,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6205,42 +6194,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6249,7 +6238,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6258,7 +6247,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6267,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6276,36 +6265,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
@@ -6318,7 +6307,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
@@ -6331,21 +6320,21 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6362,7 +6351,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (15yrs)</v>
@@ -6384,7 +6373,7 @@
         <v>-5.8810474812513162E-2</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (15yrs)</v>
@@ -6406,7 +6395,7 @@
         <v>-2.726690194899704E-2</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (15yrs)</v>
@@ -6428,7 +6417,7 @@
         <v>3.7139913387016728E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (15yrs)</v>
@@ -6450,7 +6439,7 @@
         <v>0.10276836564090074</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (15yrs)</v>
@@ -6472,16 +6461,16 @@
         <v>0.13581567914138118</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="461" t="s">
+    <row r="124" spans="2:6">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6494,7 +6483,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6503,7 +6492,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6513,30 +6502,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6545,7 +6534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6558,14 +6547,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6584,7 +6573,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6605,7 +6594,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6626,14 +6615,14 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6652,7 +6641,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6673,7 +6662,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6694,7 +6683,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6704,21 +6693,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6727,92 +6716,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6829,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6856,15 +6845,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>HKD</v>
@@ -6913,7 +6902,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6929,7 +6918,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6937,7 +6926,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6957,7 +6946,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6977,7 +6966,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -6999,7 +6988,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7019,7 +7008,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7035,7 +7024,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7051,7 +7040,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7071,7 +7060,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7087,7 +7076,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7107,7 +7096,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7127,7 +7116,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7147,7 +7136,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7167,7 +7156,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7187,13 +7176,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7215,7 +7204,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7235,7 +7224,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7251,7 +7240,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7271,7 +7260,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7291,7 +7280,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7311,7 +7300,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7339,7 +7328,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7347,7 +7336,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7369,7 +7358,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7390,7 +7379,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7411,7 +7400,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7432,7 +7421,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7453,7 +7442,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7469,12 +7458,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7523,7 +7512,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7572,7 +7561,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7621,7 +7610,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7670,7 +7659,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7719,7 +7708,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7768,7 +7757,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7817,7 +7806,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7866,7 +7855,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7915,7 +7904,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7964,7 +7953,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8013,7 +8002,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8062,7 +8051,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8111,12 +8100,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8165,7 +8154,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8214,12 +8203,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8268,7 +8257,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8317,7 +8306,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8366,7 +8355,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8415,13 +8404,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8470,7 +8459,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8519,7 +8508,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8568,7 +8557,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8617,7 +8606,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8666,12 +8655,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8721,7 +8710,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8770,7 +8759,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8820,7 +8809,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8869,7 +8858,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8919,7 +8908,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8935,13 +8924,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8990,7 +8979,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9024,7 +9013,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9058,7 +9047,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9107,7 +9096,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9188,7 +9177,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9199,7 +9188,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9215,7 +9204,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9226,7 +9215,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9246,7 +9235,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9267,7 +9256,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9288,7 +9277,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9309,7 +9298,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9330,7 +9319,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9351,7 +9340,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9372,7 +9361,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9392,7 +9381,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9404,7 +9393,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9428,12 +9417,12 @@
         <v>10301292</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9453,7 +9442,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9473,7 +9462,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9493,7 +9482,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9513,7 +9502,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9533,7 +9522,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9554,7 +9543,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9574,7 +9563,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9594,7 +9583,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9606,7 +9595,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9618,7 +9607,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9642,7 +9631,7 @@
         <v>3019689</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9659,7 +9648,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9678,7 +9667,7 @@
         <v>7044710.8499999996</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9693,7 +9682,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9712,7 +9701,7 @@
         <v>7052296.8499999996</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9728,7 +9717,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9745,7 +9734,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9765,7 +9754,7 @@
         <v>16536245.85</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9776,7 +9765,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9789,7 +9778,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9808,7 +9797,7 @@
         <v>3215264.85</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9824,7 +9813,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9840,7 +9829,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9856,7 +9845,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9875,7 +9864,7 @@
         <v>641518.70000000007</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9895,7 +9884,7 @@
         <v>13320981</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9915,7 +9904,7 @@
         <v>13134092</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9934,7 +9923,7 @@
         <v>186889</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9945,7 +9934,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9959,7 +9948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9973,7 +9962,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9988,10 +9977,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10004,7 +9993,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10018,7 +10007,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10029,10 +10018,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10044,7 +10033,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10058,7 +10047,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10072,10 +10061,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10087,7 +10076,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10098,7 +10087,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10109,10 +10098,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10124,7 +10113,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10140,7 +10129,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10151,7 +10140,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10165,7 +10154,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10181,7 +10170,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10191,7 +10180,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10201,7 +10190,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10211,7 +10200,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10221,10 +10210,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10236,7 +10225,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10252,7 +10241,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10268,7 +10257,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10281,7 +10270,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10294,10 +10283,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10309,7 +10298,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10323,7 +10312,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10337,7 +10326,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10351,7 +10340,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10365,7 +10354,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10376,7 +10365,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10384,7 +10373,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10401,7 +10390,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10418,7 +10407,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10435,7 +10424,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10471,19 +10460,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10540,7 +10529,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10563,7 +10552,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10583,7 +10572,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10640,7 +10629,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10695,7 +10684,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10750,7 +10739,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10805,7 +10794,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10862,7 +10851,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10919,7 +10908,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10974,7 +10963,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11029,7 +11018,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11084,7 +11073,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11141,7 +11130,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11198,7 +11187,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11253,7 +11242,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11308,7 +11297,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11334,7 +11323,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11359,7 +11348,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11416,7 +11405,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11435,7 +11424,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11458,7 +11447,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11479,7 +11468,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11536,7 +11525,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11593,7 +11582,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11650,7 +11639,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11707,18 +11696,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11775,7 +11764,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11833,7 +11822,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11890,7 +11879,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11945,18 +11934,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12013,18 +12002,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12079,18 +12068,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12148,10 +12137,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12174,14 +12163,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12236,7 +12225,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12291,7 +12280,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12348,7 +12337,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12403,11 +12392,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12417,7 +12406,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12441,7 +12430,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12465,7 +12454,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12520,11 +12509,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12534,7 +12523,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12589,7 +12578,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12644,7 +12633,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12699,7 +12688,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12754,7 +12743,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12810,7 +12799,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12865,11 +12854,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12879,7 +12868,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12904,7 +12893,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12929,7 +12918,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12954,7 +12943,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12981,10 +12970,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13007,7 +12996,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13028,7 +13017,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13085,7 +13074,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13142,7 +13131,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13199,7 +13188,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13256,7 +13245,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13313,7 +13302,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13370,7 +13359,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13427,7 +13416,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13484,7 +13473,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13542,7 +13531,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13599,7 +13588,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13656,7 +13645,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13715,7 +13704,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13741,7 +13730,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13765,7 +13754,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13822,18 +13811,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13889,7 +13878,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13945,7 +13934,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14000,7 +13989,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14021,23 +14010,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2161616161616162E-2</v>
+        <v>3.2489795918367349E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2161616161616162E-2</v>
+        <v>3.2489795918367349E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1979797979797973E-2</v>
+        <v>5.2510204081632643E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14076,11 +14065,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14101,7 +14090,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14158,7 +14147,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14215,10 +14204,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14241,7 +14230,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14251,7 +14240,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14308,7 +14297,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14365,7 +14354,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14422,7 +14411,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14479,7 +14468,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14536,11 +14525,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14563,7 +14552,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14620,7 +14609,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14677,7 +14666,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14704,18 +14693,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14769,7 +14758,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14824,11 +14813,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14887,7 +14876,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14945,7 +14934,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15002,7 +14991,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15061,7 +15050,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15121,7 +15110,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15140,7 +15129,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15163,7 +15152,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15184,7 +15173,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15242,25 +15231,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.2668281083272867E-2</v>
+        <v>6.3307753339224629E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.122870186343727E-2</v>
+        <v>6.1853484535513162E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7141401921018589E-2</v>
+        <v>5.7724477450824901E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15299,18 +15288,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4084724452291695E-2</v>
+        <v>7.4840691028335474E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8175699109062959E-2</v>
+        <v>6.8871369508135022E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15349,688 +15338,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16052,16 +16041,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16076,7 +16065,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16091,7 +16080,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16123,7 +16112,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16151,7 +16140,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16184,7 +16173,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16214,7 +16203,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16249,7 +16238,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*HKD</v>
@@ -16275,7 +16264,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
@@ -16297,7 +16286,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
@@ -16313,7 +16302,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16328,7 +16317,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16346,7 +16335,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16371,7 +16360,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16387,7 +16376,7 @@
         <v>3.4071209167200502E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>549</v>
       </c>
@@ -16406,7 +16395,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16433,10 +16422,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16475,7 +16464,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16524,7 +16513,7 @@
         <v>3530214.9669478289</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16573,7 +16562,7 @@
         <v>3403723.6918339306</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16630,7 +16619,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16687,7 +16676,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16744,7 +16733,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16793,7 +16782,7 @@
         <v>2941486.6418798994</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16842,7 +16831,7 @@
         <v>2836090.1151682204</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16891,7 +16880,7 @@
         <v>2734470.0556635396</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16940,7 +16929,7 @@
         <v>2636491.148616781</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16989,7 +16978,7 @@
         <v>2542022.9277471104</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17038,7 +17027,7 @@
         <v>2450939.6015162719</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17087,7 +17076,7 @@
         <v>2363119.8856276996</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17144,7 +17133,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17201,7 +17190,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17258,7 +17247,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17307,7 +17296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17356,7 +17345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17405,7 +17394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17454,7 +17443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17503,7 +17492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17552,7 +17541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17601,7 +17590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17650,7 +17639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17699,7 +17688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17748,7 +17737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17797,7 +17786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17854,7 +17843,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17911,7 +17900,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17968,7 +17957,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18025,7 +18014,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18071,7 +18060,7 @@
         <v>29799388.838375315</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18084,10 +18073,10 @@
         <v>71328036.646042943</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18102,7 +18091,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>71328036.646042943</v>
@@ -18134,7 +18123,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18161,7 +18150,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18187,7 +18176,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18213,7 +18202,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18239,7 +18228,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18265,7 +18254,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18291,7 +18280,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18317,7 +18306,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18343,7 +18332,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18369,7 +18358,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18395,7 +18384,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18430,7 +18419,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18465,7 +18454,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18500,7 +18489,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18535,7 +18524,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18556,7 +18545,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18580,7 +18569,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18608,7 +18597,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18639,7 +18628,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18670,7 +18659,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18701,7 +18690,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18732,7 +18721,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18763,7 +18752,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -18794,7 +18783,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -18825,7 +18814,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -18857,7 +18846,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -18888,7 +18877,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -18920,7 +18909,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -18952,7 +18941,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -18984,7 +18973,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -19016,7 +19005,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19048,7 +19037,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19080,7 +19069,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19103,7 +19092,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19131,7 +19120,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19159,7 +19148,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19187,7 +19176,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19215,7 +19204,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19243,7 +19232,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19256,16 +19245,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19277,7 +19266,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19289,7 +19278,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19301,7 +19290,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19313,7 +19302,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19353,14 +19342,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19370,7 +19359,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19379,7 +19368,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19400,14 +19389,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19420,7 +19409,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19433,7 +19422,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19446,7 +19435,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19459,14 +19448,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19476,7 +19465,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19489,7 +19478,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19502,7 +19491,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19515,7 +19504,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19525,7 +19514,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19533,7 +19522,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19545,18 +19534,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19577,7 +19566,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19601,7 +19590,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19624,7 +19613,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19647,7 +19636,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
@@ -19661,12 +19650,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19687,7 +19676,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19710,7 +19699,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19733,16 +19722,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19762,13 +19751,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.95</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19779,10 +19768,10 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13150443474697285</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.13544831512510774</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
@@ -19802,7 +19791,7 @@
         <v>2.4767426927084515E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
@@ -19821,7 +19810,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19831,7 +19820,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19840,7 +19829,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>550</v>
       </c>
@@ -19852,7 +19841,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19862,7 +19851,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19872,7 +19861,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19880,7 +19869,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19893,7 +19882,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19905,7 +19894,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -19921,7 +19910,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19933,7 +19922,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19943,7 +19932,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19955,7 +19944,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19965,7 +19954,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19981,7 +19970,7 @@
         <v>8.8521421695043054E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19991,12 +19980,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20006,7 +19995,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20019,13 +20008,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20046,7 +20035,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20071,7 +20060,7 @@
         <v>0.49521704363132646</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20096,7 +20085,7 @@
         <v>0.37184400405652518</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20117,7 +20106,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20142,7 +20131,7 @@
         <v>0.22528831503764324</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20183,7 +20172,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20192,7 +20181,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20206,7 +20195,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>541</v>
       </c>
@@ -20215,7 +20204,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>533</v>
       </c>
@@ -20232,7 +20221,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20248,7 +20237,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20258,7 +20247,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20269,16 +20258,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20287,43 +20276,43 @@
         <v>11803071135</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>58425.202118250003</v>
+        <v>57835.048561500007</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.13150443474697285</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.13544831512510774</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20339,7 +20328,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20355,7 +20344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>534</v>
       </c>
@@ -20371,7 +20360,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
@@ -20388,7 +20377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20404,11 +20393,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20424,7 +20413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
@@ -20440,7 +20429,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
@@ -20456,7 +20445,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
@@ -20472,7 +20461,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
@@ -20488,7 +20477,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20498,25 +20487,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20525,7 +20514,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>500</v>
       </c>
@@ -20534,7 +20523,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20547,11 +20536,11 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>501</v>
       </c>
@@ -20560,7 +20549,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20573,7 +20562,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20586,7 +20575,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>502</v>
       </c>
@@ -20595,7 +20584,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20608,7 +20597,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>503</v>
       </c>
@@ -20617,7 +20606,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20632,7 +20621,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20647,7 +20636,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20660,12 +20649,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20678,7 +20667,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>505</v>
       </c>
@@ -20687,7 +20676,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20700,16 +20689,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20722,25 +20711,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20753,7 +20742,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20766,23 +20755,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.2668281083272867E-2</v>
+        <v>6.3307753339224629E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2161616161616162E-2</v>
+        <v>3.2489795918367349E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20792,7 +20781,7 @@
         <v>0.5132040580286571</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20803,7 +20792,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20816,7 +20805,7 @@
         <v>0.28020929484316204</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20830,7 +20819,7 @@
         <v>0.21248573712552665</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20844,7 +20833,7 @@
         <v>0.86056930273853416</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20858,7 +20847,7 @@
         <v>1.532381509863507</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20868,43 +20857,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20917,7 +20906,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -20930,7 +20919,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20939,7 +20928,7 @@
         <v>0.27351475277205878</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20948,12 +20937,12 @@
         <v>0.94608729427783522</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20966,7 +20955,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -20979,7 +20968,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -20992,12 +20981,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21010,7 +20999,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21023,7 +21012,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
@@ -21036,7 +21025,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21046,49 +21035,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21098,7 +21087,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21108,7 +21097,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21118,7 +21107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>534</v>
@@ -21127,47 +21116,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
@@ -21181,7 +21170,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
@@ -21195,29 +21184,29 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21235,7 +21224,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21258,7 +21247,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21281,7 +21270,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21303,7 +21292,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21325,7 +21314,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21347,7 +21336,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>518</v>
       </c>
@@ -21356,7 +21345,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21369,16 +21358,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21388,30 +21377,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21420,7 +21409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21433,14 +21422,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21459,7 +21448,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21480,7 +21469,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21501,7 +21490,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21520,7 +21509,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21541,7 +21530,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21562,7 +21551,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21572,50 +21561,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21624,60 +21613,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21692,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D01B309-324E-45C5-9A3E-4329EE14C115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B2F9F3-9CE2-412C-A7FB-F6B77338BD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.9000000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>57835.048561500007</v>
+        <v>56064.587891249997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13544831512510774</v>
+        <v>0.14761570667804591</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.3307753339224629E-2</v>
+        <v>6.530694554993699E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.2489795918367349E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.2489795918367349E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.2489795918367349E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.2510204081632643E-2</v>
+        <v>5.4168421052631574E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.3307753339224629E-2</v>
+        <v>6.530694554993699E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.1853484535513162E-2</v>
+        <v>6.3806752468213587E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7724477450824901E-2</v>
+        <v>5.9547355686114113E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4840691028335474E-2</v>
+        <v>7.7204081271335545E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8871369508135022E-2</v>
+        <v>7.1046254861023506E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.9000000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13544831512510774</v>
+        <v>0.14761570667804591</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.9000000000000004</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>57835.048561500007</v>
+        <v>56064.587891249997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.13544831512510774</v>
+        <v>0.14761570667804591</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.3307753339224629E-2</v>
+        <v>6.530694554993699E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.2489795918367349E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B2F9F3-9CE2-412C-A7FB-F6B77338BD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EC70C0-572B-47FD-BA21-57E083399FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.75</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>56064.587891249997</v>
+        <v>55356.403623149999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14761570667804591</v>
+        <v>0.15262981708994752</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.530694554993699E-2</v>
+        <v>6.6142428861876476E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3944562899786777E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3944562899786777E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3944562899786777E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4168421052631574E-2</v>
+        <v>5.4861407249466941E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.530694554993699E-2</v>
+        <v>6.6142428861876476E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.3806752468213587E-2</v>
+        <v>6.4623043544565995E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.9547355686114113E-2</v>
+        <v>6.0309155545637955E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7204081271335545E-2</v>
+        <v>7.8191766746022143E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1046254861023506E-2</v>
+        <v>7.1955162172678389E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.75</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14761570667804591</v>
+        <v>0.15262981708994752</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.75</v>
+        <v>4.6900000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>56064.587891249997</v>
+        <v>55356.403623149999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14761570667804591</v>
+        <v>0.15262981708994752</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.530694554993699E-2</v>
+        <v>6.6142428861876476E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3944562899786777E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EC70C0-572B-47FD-BA21-57E083399FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D340098-1730-49BD-9375-7EC87C255E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,39 +4986,48 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.6900000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55356.403623149999</v>
+        <v>56064.587891249997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15262981708994752</v>
+        <v>0.14761570667804591</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="464"/>
-      <c r="D54" s="464"/>
-      <c r="E54" s="464"/>
-      <c r="F54" s="464"/>
+      <c r="C54" s="465"/>
+      <c r="D54" s="465"/>
+      <c r="E54" s="465"/>
+      <c r="F54" s="465"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6142428861876476E-2</v>
+        <v>6.530694554993699E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6484,13 +6484,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="465" t="s">
+      <c r="B127" s="466" t="s">
         <v>358</v>
       </c>
-      <c r="C127" s="465"/>
-      <c r="D127" s="465"/>
-      <c r="E127" s="465"/>
-      <c r="F127" s="465"/>
+      <c r="C127" s="466"/>
+      <c r="D127" s="466"/>
+      <c r="E127" s="466"/>
+      <c r="F127" s="466"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6708,13 +6708,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="464" t="s">
+      <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="464"/>
-      <c r="D152" s="464"/>
-      <c r="E152" s="464"/>
-      <c r="F152" s="464"/>
+      <c r="C152" s="465"/>
+      <c r="D152" s="465"/>
+      <c r="E152" s="465"/>
+      <c r="F152" s="465"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4861407249466941E-2</v>
+        <v>5.4168421052631574E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6142428861876476E-2</v>
+        <v>6.530694554993699E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4623043544565995E-2</v>
+        <v>6.3806752468213587E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0309155545637955E-2</v>
+        <v>5.9547355686114113E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8191766746022143E-2</v>
+        <v>7.7204081271335545E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1955162172678389E-2</v>
+        <v>7.1046254861023506E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18064,10 +18064,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="468" t="s">
+      <c r="J52" s="460" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="468"/>
+      <c r="K52" s="460"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>71328036.646042943</v>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.6900000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15262981708994752</v>
+        <v>0.14761570667804591</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.6900000000000004</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55356.403623149999</v>
+        <v>56064.587891249997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15262981708994752</v>
+        <v>0.14761570667804591</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6142428861876476E-2</v>
+        <v>6.530694554993699E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3944562899786777E-2</v>
+        <v>3.3515789473684214E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D340098-1730-49BD-9375-7EC87C255E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7146FCE2-0F64-47C4-BF85-7E5D8DF9F783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,55 +4989,55 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>56064.587891249997</v>
+        <v>55474.434334500002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14761570667804591</v>
+        <v>0.15178809681138061</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.530694554993699E-2</v>
+        <v>6.6001700289829934E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3872340425531916E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3872340425531916E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3872340425531916E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4168421052631574E-2</v>
+        <v>5.4744680851063821E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.530694554993699E-2</v>
+        <v>6.6001700289829934E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.3806752468213587E-2</v>
+        <v>6.448554770723712E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.9547355686114113E-2</v>
+        <v>6.0180838193413196E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7204081271335545E-2</v>
+        <v>7.8025401284860393E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1046254861023506E-2</v>
+        <v>7.1802066082949284E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14761570667804591</v>
+        <v>0.15178809681138061</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>56064.587891249997</v>
+        <v>55474.434334500002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14761570667804591</v>
+        <v>0.15178809681138061</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.530694554993699E-2</v>
+        <v>6.6001700289829934E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3515789473684214E-2</v>
+        <v>3.3872340425531916E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7146FCE2-0F64-47C4-BF85-7E5D8DF9F783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC9A817-31B0-4C1B-B6F4-F225D026BE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,36 +4989,45 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.7</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55474.434334500002</v>
+        <v>56300.649313949994</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15178809681138061</v>
+        <v>0.14596342489630992</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5555,13 +5555,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.3455729956390798</v>
+        <v>3.3058505032532972</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5570,13 +5570,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.1632581103676909</v>
+        <v>4.170852752110819</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6001700289829934E-2</v>
+        <v>6.5033121878868075E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3872340425531916E-2</v>
+        <v>3.3375262054507339E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6579,19 +6579,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.29131237091673101</v>
+        <v>0.28912517068730093</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0542606247223487</v>
+        <v>3.0167253325659962</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.3455729956390798</v>
+        <v>3.3058505032532972</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6600,19 +6600,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.33495742840523723</v>
+        <v>0.33535185185185185</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8283006819624537</v>
+        <v>3.8355009002589671</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.1632581103676909</v>
+        <v>4.170852752110819</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3872340425531916E-2</v>
+        <v>3.3375262054507339E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3872340425531916E-2</v>
+        <v>3.3375262054507339E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4744680851063821E-2</v>
+        <v>5.3941299790356396E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6001700289829934E-2</v>
+        <v>6.5033121878868075E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.448554770723712E-2</v>
+        <v>6.3539218914887743E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0180838193413196E-2</v>
+        <v>5.9297681238792886E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8025401284860393E-2</v>
+        <v>7.6880374431623461E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1802066082949284E-2</v>
+        <v>7.0748366999971002E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.7</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15178809681138061</v>
+        <v>0.14596342489630992</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20041,23 +20041,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.29131237091673101</v>
+        <v>0.28912517068730093</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0542606247223487</v>
+        <v>3.0167253325659962</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.3455729956390798</v>
+        <v>3.3058505032532972</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.49521704363132646</v>
+        <v>0.50121040774771664</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20066,23 +20066,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.33495742840523723</v>
+        <v>0.33535185185185185</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8283006819624537</v>
+        <v>3.8355009002589671</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.1632581103676909</v>
+        <v>4.170852752110819</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.37184400405652518</v>
+        <v>0.37069811792083063</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.7</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55474.434334500002</v>
+        <v>56300.649313949994</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15178809681138061</v>
+        <v>0.14596342489630992</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20419,14 +20419,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.3455729956390798</v>
+        <v>3.3058505032532972</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20435,14 +20435,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.1632581103676909</v>
+        <v>4.170852752110819</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6001700289829934E-2</v>
+        <v>6.5033121878868075E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3872340425531916E-2</v>
+        <v>3.3375262054507339E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21454,19 +21454,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.29131237091673101</v>
+        <v>0.28912517068730093</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0542606247223487</v>
+        <v>3.0167253325659962</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.3455729956390798</v>
+        <v>3.3058505032532972</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21475,19 +21475,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.33495742840523723</v>
+        <v>0.33535185185185185</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8283006819624537</v>
+        <v>3.8355009002589671</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.1632581103676909</v>
+        <v>4.170852752110819</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC9A817-31B0-4C1B-B6F4-F225D026BE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EC305A-9158-4574-BD6B-FFACFC9D2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,55 +4989,55 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.7699999999999996</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>56300.649313949994</v>
+        <v>55828.526468550001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14596342489630992</v>
+        <v>0.14927746889065724</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.5033121878868075E-2</v>
+        <v>6.5583084854587886E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3375262054507339E-2</v>
+        <v>3.3657505285412261E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3375262054507339E-2</v>
+        <v>3.3657505285412261E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3375262054507339E-2</v>
+        <v>3.3657505285412261E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.3941299790356396E-2</v>
+        <v>5.4397463002114156E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5033121878868075E-2</v>
+        <v>6.5583084854587886E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.3539218914887743E-2</v>
+        <v>6.4076548461736674E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.9297681238792886E-2</v>
+        <v>5.979914154525201E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6880374431623461E-2</v>
+        <v>7.7530525589607574E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0748366999971002E-2</v>
+        <v>7.1346661858321697E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.7699999999999996</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14596342489630992</v>
+        <v>0.14927746889065724</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.7699999999999996</v>
+        <v>4.7300000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>56300.649313949994</v>
+        <v>55828.526468550001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14596342489630992</v>
+        <v>0.14927746889065724</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.5033121878868075E-2</v>
+        <v>6.5583084854587886E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3375262054507339E-2</v>
+        <v>3.3657505285412261E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EC305A-9158-4574-BD6B-FFACFC9D2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77DEE27-8DCB-4D2A-9C58-31DF91053146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,36 +4989,45 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77DEE27-8DCB-4D2A-9C58-31DF91053146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF69CFD-E4C1-42E0-972E-DA507ACE365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,55 +4989,55 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF69CFD-E4C1-42E0-972E-DA507ACE365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70734E3A-C6B0-4B6F-8506-19D6DE36FDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,36 +4989,45 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.7300000000000004</v>
+        <v>4.53</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55828.526468550001</v>
+        <v>53467.912241550002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14927746889065724</v>
+        <v>0.16643817544217571</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.5583084854587886E-2</v>
+        <v>6.8478585289669033E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3657505285412261E-2</v>
+        <v>3.5143487858719645E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3657505285412261E-2</v>
+        <v>3.5143487858719645E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3657505285412261E-2</v>
+        <v>3.5143487858719645E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4397463002114156E-2</v>
+        <v>5.6799116997792484E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5583084854587886E-2</v>
+        <v>6.8478585289669033E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4076548461736674E-2</v>
+        <v>6.6905535148789066E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.979914154525201E-2</v>
+        <v>6.2439280244821635E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7530525589607574E-2</v>
+        <v>8.0953506851841911E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1346661858321697E-2</v>
+        <v>7.4496624854274093E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.7300000000000004</v>
+        <v>4.53</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14927746889065724</v>
+        <v>0.16643817544217571</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.7300000000000004</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55828.526468550001</v>
+        <v>53467.912241550002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14927746889065724</v>
+        <v>0.16643817544217571</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.5583084854587886E-2</v>
+        <v>6.8478585289669033E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3657505285412261E-2</v>
+        <v>3.5143487858719645E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70734E3A-C6B0-4B6F-8506-19D6DE36FDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEC3DA3-8E0C-4C56-9D25-4C154E6A0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEC3DA3-8E0C-4C56-9D25-4C154E6A0995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CBCC30-B474-4174-937B-B2A3CF75078D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,55 +4989,55 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.53</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>53467.912241550002</v>
+        <v>54294.127220999995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16643817544217571</v>
+        <v>0.16031672131726196</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8478585289669033E-2</v>
+        <v>6.7436519861347993E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5143487858719645E-2</v>
+        <v>3.4608695652173921E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5143487858719645E-2</v>
+        <v>3.4608695652173921E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5143487858719645E-2</v>
+        <v>3.4608695652173921E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.6799116997792484E-2</v>
+        <v>5.5934782608695652E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8478585289669033E-2</v>
+        <v>6.7436519861347993E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6905535148789066E-2</v>
+        <v>6.5887407440003154E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2439280244821635E-2</v>
+        <v>6.148911728457436E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0953506851841911E-2</v>
+        <v>7.9721605660618242E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4496624854274093E-2</v>
+        <v>7.3362980563013422E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.53</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16643817544217571</v>
+        <v>0.16031672131726196</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.53</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>53467.912241550002</v>
+        <v>54294.127220999995</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16643817544217571</v>
+        <v>0.16031672131726196</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8478585289669033E-2</v>
+        <v>6.7436519861347993E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5143487858719645E-2</v>
+        <v>3.4608695652173921E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CBCC30-B474-4174-937B-B2A3CF75078D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCA8B9B-BB71-4F87-9861-B0D752C89308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,36 +4989,45 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>4.5999999999999996</v>
+        <v>4.54</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>54294.127220999995</v>
+        <v>53585.942952900004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16031672131726196</v>
+        <v>0.16555583542529126</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7436519861347993E-2</v>
+        <v>6.8327751401365794E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4608695652173921E-2</v>
+        <v>3.5066079295154186E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4608695652173921E-2</v>
+        <v>3.5066079295154186E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4608695652173921E-2</v>
+        <v>3.5066079295154186E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5934782608695652E-2</v>
+        <v>5.6674008810572683E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7436519861347993E-2</v>
+        <v>6.8327751401365794E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5887407440003154E-2</v>
+        <v>6.6758166128637553E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.148911728457436E-2</v>
+        <v>6.2301748790537889E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9721605660618242E-2</v>
+        <v>8.077519516274094E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3362980563013422E-2</v>
+        <v>7.4332535372216221E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.5999999999999996</v>
+        <v>4.54</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16031672131726196</v>
+        <v>0.16555583542529126</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.5999999999999996</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>54294.127220999995</v>
+        <v>53585.942952900004</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16031672131726196</v>
+        <v>0.16555583542529126</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7436519861347993E-2</v>
+        <v>6.8327751401365794E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4608695652173921E-2</v>
+        <v>3.5066079295154186E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCA8B9B-BB71-4F87-9861-B0D752C89308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520F7135-C9D5-48E5-A778-53BFF3EF1BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Other LT liabilities</t>
-  </si>
-  <si>
-    <t>Biological assets</t>
   </si>
   <si>
     <t>Intangible assets</t>
@@ -3256,6 +3253,9 @@
   </si>
   <si>
     <t>Sales/Total Assets g Projection</t>
+  </si>
+  <si>
+    <t>Biological/Mineral assets</t>
   </si>
   <si>
     <t>中國旺旺</t>
@@ -4986,58 +4986,58 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5335,7 +5335,7 @@
   <sheetData>
     <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F3" s="429">
         <v>46044</v>
@@ -5356,64 +5356,64 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C4" s="420" t="s">
         <v>555</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F4" s="431" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>556</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C9" s="48">
         <v>11803071135</v>
@@ -5421,18 +5421,18 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>53585.942952900004</v>
+        <v>55592.465045849996</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16555583542529126</v>
+        <v>0.15094880681171671</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="B12" s="462" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5457,13 +5457,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E15" s="253" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5472,13 +5472,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E16" s="416">
         <v>1</v>
@@ -5486,16 +5486,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C17" s="456">
         <v>0.02</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5508,7 +5508,7 @@
         <v>6.6277455556474951</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E18" s="418">
         <v>6</v>
@@ -5516,14 +5516,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Terminal_Growth&lt;2%, "Lower than Inflation rate", IF(Terminal_Growth&lt;5%, "Low growth", IF(Terminal_Growth&lt;8%, "Medium growth", "High growth")))</f>
         <v>Low growth</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E19" s="419">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5536,14 +5536,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C21" s="254" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E21" s="442">
         <v>3</v>
@@ -5551,14 +5551,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
         <v>3.3058505032532972</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E22" s="79">
         <v>0.3</v>
@@ -5566,14 +5566,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
         <v>4.170852752110819</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E23" s="443">
         <v>0.2</v>
@@ -5581,14 +5581,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
         <v>5.1345919269174427</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E24" s="443">
         <v>0.1174</v>
@@ -5596,14 +5596,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
         <v>5.7883592149489207</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E25" s="444">
         <v>7.2499999999999995E-2</v>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5624,26 +5624,26 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
-        <v>356</v>
-      </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="B29" s="462" t="s">
+        <v>355</v>
+      </c>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="B30" s="466" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C32" s="105">
         <f>scaling_factor</f>
@@ -5651,17 +5651,17 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
-        <v>196</v>
-      </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="B33" s="463" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
@@ -5677,17 +5677,17 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
-        <v>198</v>
-      </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="B36" s="463" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="285">
         <f>Normalized_FCF!C15</f>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
@@ -5712,17 +5712,17 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="B40" s="463" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="285">
         <f>Normalized_FCF!C9</f>
@@ -5734,17 +5734,17 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
-        <v>205</v>
-      </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="B43" s="463" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="286">
         <f>Normalized_FCF!C45</f>
@@ -5774,7 +5774,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
@@ -5787,12 +5787,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="285">
         <f>Normalized_FCF!C13</f>
@@ -5804,17 +5804,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
-        <v>206</v>
-      </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="B51" s="463" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
@@ -5826,17 +5826,17 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="465"/>
-      <c r="D54" s="465"/>
-      <c r="E54" s="465"/>
-      <c r="F54" s="465"/>
+      <c r="B54" s="463" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" s="464"/>
+      <c r="D54" s="464"/>
+      <c r="E54" s="464"/>
+      <c r="F54" s="464"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="285">
         <f>Normalized_FCF!C17</f>
@@ -5848,26 +5848,26 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
-        <v>270</v>
-      </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="B57" s="462" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
-        <v>282</v>
-      </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="B58" s="462" t="s">
+        <v>281</v>
+      </c>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
@@ -5893,24 +5893,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8327751401365794E-2</v>
+        <v>6.5861569291337727E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5066079295154186E-2</v>
+        <v>3.3800424628450107E-2</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
@@ -5919,18 +5919,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C65" s="264" t="s">
+        <v>326</v>
+      </c>
+      <c r="D65" s="264" t="s">
         <v>327</v>
-      </c>
-      <c r="D65" s="264" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5998,18 +5998,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
-        <v>478</v>
-      </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="B73" s="462" t="s">
+        <v>477</v>
+      </c>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6018,23 +6018,23 @@
     <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="B77" s="462" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="285">
         <f>DCF!F4</f>
@@ -6048,7 +6048,7 @@
     <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6062,7 +6062,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="337">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6072,7 +6072,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6085,13 +6085,13 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
@@ -6105,7 +6105,7 @@
     <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="291">
         <f>BS!C66</f>
@@ -6119,7 +6119,7 @@
     <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6136,13 +6136,13 @@
     <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="285">
         <f>DCF!F6</f>
@@ -6156,7 +6156,7 @@
     <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6173,7 +6173,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6198,40 +6198,40 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
-        <v>485</v>
-      </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="B96" s="462" t="s">
+        <v>484</v>
+      </c>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
-        <v>484</v>
-      </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="B97" s="466" t="s">
+        <v>483</v>
+      </c>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
-        <v>483</v>
-      </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="B98" s="466" t="s">
+        <v>482</v>
+      </c>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C102" s="263">
         <f>E25</f>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C103" s="263">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C104" s="211">
         <f>Terminal_Growth</f>
@@ -6267,36 +6267,36 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="462" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
-        <v>284</v>
-      </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
@@ -6321,34 +6321,34 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
-        <v>491</v>
-      </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="B114" s="462" t="s">
+        <v>490</v>
+      </c>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C117" s="342" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D117" s="342" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E117" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6462,17 +6462,17 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
-        <v>357</v>
-      </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="B124" s="463" t="s">
+        <v>356</v>
+      </c>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
@@ -6484,17 +6484,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="466" t="s">
-        <v>358</v>
-      </c>
-      <c r="C127" s="466"/>
-      <c r="D127" s="466"/>
-      <c r="E127" s="466"/>
-      <c r="F127" s="466"/>
+      <c r="B127" s="465" t="s">
+        <v>357</v>
+      </c>
+      <c r="C127" s="465"/>
+      <c r="D127" s="465"/>
+      <c r="E127" s="465"/>
+      <c r="F127" s="465"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6503,31 +6503,31 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
-        <v>285</v>
-      </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="B131" s="467" t="s">
+        <v>284</v>
+      </c>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
-        <v>359</v>
-      </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="B132" s="462" t="s">
+        <v>358</v>
+      </c>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C135" s="202">
         <f>E21</f>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
@@ -6549,33 +6549,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
@@ -6624,26 +6624,26 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6694,114 +6694,102 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
-        <v>360</v>
-      </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="B149" s="461" t="s">
+        <v>359</v>
+      </c>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="465" t="s">
-        <v>293</v>
-      </c>
-      <c r="C152" s="465"/>
-      <c r="D152" s="465"/>
-      <c r="E152" s="465"/>
-      <c r="F152" s="465"/>
+      <c r="B152" s="464" t="s">
+        <v>292</v>
+      </c>
+      <c r="C152" s="464"/>
+      <c r="D152" s="464"/>
+      <c r="E152" s="464"/>
+      <c r="F152" s="464"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
-        <v>438</v>
-      </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="B158" s="463" t="s">
+        <v>437</v>
+      </c>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="460" t="s">
+        <v>293</v>
+      </c>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
-        <v>295</v>
-      </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6904,7 +6904,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="103">
         <v>1000</v>
@@ -6948,7 +6948,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="287">
         <v>12321539</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="287">
         <f>3008125+C7</f>
@@ -6990,7 +6990,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="288">
         <v>3026852</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="287"/>
       <c r="D8" s="287"/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="287"/>
       <c r="D9" s="287"/>
@@ -7042,7 +7042,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="287">
         <v>67</v>
@@ -7062,7 +7062,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="287"/>
       <c r="D11" s="287"/>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="287">
         <v>176233</v>
@@ -7098,7 +7098,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="287">
         <v>78393</v>
@@ -7118,7 +7118,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="287">
         <v>1411247</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="289">
         <v>4328415</v>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="287">
         <v>7150</v>
@@ -7178,13 +7178,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="287">
         <f>749602+165519+4880+1600</f>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="287">
         <v>633455</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C22" s="287">
         <v>4161620</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C23" s="287">
         <v>-47985</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" s="287">
         <v>-4160974</v>
@@ -7330,15 +7330,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="270">
         <f>BS!C4</f>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="270">
         <f>BS!C6</f>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="271">
         <f>BS!C33+BS!C42</f>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="271">
         <f>BS!G27</f>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C32" s="270">
         <f>BS!G28</f>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
@@ -7460,7 +7460,7 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -7514,7 +7514,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="270">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="267">
         <f>IF(C36="","",C36+C37)</f>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="270">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7661,7 +7661,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="282">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="282">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7759,7 +7759,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="270">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="271">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" s="290">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="285">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7955,7 +7955,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="270">
         <f>IF(C$4="","",-C14)</f>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="271">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -8053,7 +8053,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="270">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -8102,12 +8102,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="270">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="270">
         <f>IF(C$4="","",C13)</f>
@@ -8205,12 +8205,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="285">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -8259,7 +8259,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="285">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -8308,7 +8308,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" s="285">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -8357,7 +8357,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="285">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -8406,13 +8406,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="270">
         <f>IF(C$4="","",-C19)</f>
@@ -8461,7 +8461,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" s="270">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="270">
         <f>IF(C$4="","",-C21)</f>
@@ -8559,7 +8559,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="270">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8608,7 +8608,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
@@ -8657,7 +8657,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8712,7 +8712,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="89">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="C70" s="98">
         <f>IF(D$36="","",C43/D43-1)</f>
-        <v>4.621073401912601E-2</v>
+        <v>4.6210734019126232E-2</v>
       </c>
       <c r="D70" s="98" t="str">
         <f t="shared" ref="D70:M70" si="36">IF(E$36="","",D43/E43-1)</f>
@@ -8811,7 +8811,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C71" s="98">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8910,7 +8910,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
@@ -8926,7 +8926,7 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="9"/>
     </row>
@@ -8981,7 +8981,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="260">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -9015,7 +9015,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="260">
         <f t="shared" si="40"/>
@@ -9049,7 +9049,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="259">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -9098,7 +9098,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="259">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -9190,7 +9190,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="96">
         <v>45930</v>
@@ -9206,7 +9206,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -9217,27 +9217,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="165" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="164" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="165" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H3" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18">
         <v>960113</v>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="18">
         <v>11445880</v>
@@ -9258,7 +9258,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="18">
         <v>0</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="18">
         <v>0</v>
@@ -9300,7 +9300,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="18">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18">
         <v>0</v>
@@ -9342,7 +9342,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="18">
         <v>1181728</v>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
@@ -9372,7 +9372,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9395,7 +9395,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="78">
         <f>SUM(C4:C11)</f>
@@ -9406,7 +9406,7 @@
         <v>2068010.6</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="78">
         <f>SUM(G4:G10)</f>
@@ -9424,27 +9424,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -9453,7 +9453,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="18">
         <v>3541000</v>
@@ -9464,7 +9464,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -9473,7 +9473,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="18">
         <v>283005</v>
@@ -9504,7 +9504,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G18" s="18">
         <v>0</v>
@@ -9524,7 +9524,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="18">
         <f>5440322+974865</f>
@@ -9534,7 +9534,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G19" s="18">
         <v>142790</v>
@@ -9545,7 +9545,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>554</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -9554,7 +9554,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G20" s="18">
         <v>0</v>
@@ -9565,7 +9565,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="18">
         <v>13489</v>
@@ -9574,7 +9574,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="18">
         <v>28070</v>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="18">
         <v>561179</v>
@@ -9597,7 +9597,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="18">
         <v>0</v>
@@ -9609,7 +9609,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="78">
         <f>SUM(C15:C23)</f>
@@ -9620,7 +9620,7 @@
         <v>1147254.25</v>
       </c>
       <c r="F24" s="77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="78">
         <f>SUM(G15:G21)</f>
@@ -9633,19 +9633,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="167" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H26" s="168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
@@ -9656,7 +9656,7 @@
         <v>3966210</v>
       </c>
       <c r="F27" s="169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="82">
         <f>G32-G30</f>
@@ -9675,7 +9675,7 @@
         <v>115242</v>
       </c>
       <c r="F28" s="171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G28" s="287">
         <v>-7586</v>
@@ -9690,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9709,7 +9709,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="169" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="82">
         <f>C33+C42</f>
@@ -9719,14 +9719,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" s="78">
         <f>SUM(C27:C30)</f>
         <v>4081452</v>
       </c>
       <c r="F31" s="172" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="173">
         <f>C31+C40</f>
@@ -9743,7 +9743,7 @@
         <v>4400914</v>
       </c>
       <c r="F32" s="174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="175">
         <f>G35+G40</f>
@@ -9769,24 +9769,24 @@
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" s="179" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H34" s="180" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F35" s="181" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="175">
         <f>C12+C24</f>
@@ -9805,7 +9805,7 @@
         <v>700178</v>
       </c>
       <c r="F36" s="172" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="173">
         <f>C4+C15</f>
@@ -9821,7 +9821,7 @@
         <v>94713</v>
       </c>
       <c r="F37" s="172" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="173">
         <f>C6</f>
@@ -9837,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="172" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G38" s="173">
         <f>C7+C17</f>
@@ -9853,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="173">
         <f>C7+C17+C19+C20</f>
@@ -9866,14 +9866,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="78">
         <f>SUM(C36:C39)</f>
         <v>794891</v>
       </c>
       <c r="F40" s="181" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="175">
         <f>G12+G24</f>
@@ -9893,7 +9893,7 @@
         <v>214278</v>
       </c>
       <c r="F41" s="172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G41" s="173">
         <f>C70</f>
@@ -9906,13 +9906,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C42" s="81">
         <v>1009169</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="184">
         <f>C82</f>
@@ -9925,7 +9925,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
@@ -9936,21 +9936,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" s="164" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F45" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C46" s="73">
         <f>G29</f>
@@ -9982,20 +9982,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
@@ -10009,7 +10009,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="163"/>
       <c r="D51" s="89">
@@ -10023,19 +10023,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F53" s="223"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
@@ -10049,7 +10049,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="89">
         <f>Normalized_FCF!C9/G40</f>
@@ -10066,19 +10066,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57" s="223"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
@@ -10089,7 +10089,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="95"/>
       <c r="D59" s="89">
@@ -10103,19 +10103,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C61" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F61" s="223"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C62" s="89">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -10126,12 +10126,12 @@
         <v>-4.2531881530600527E-4</v>
       </c>
       <c r="F62" s="223" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -10142,21 +10142,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65" s="165" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C66" s="19">
         <f>G4+G5+G15</f>
@@ -10167,12 +10167,12 @@
         <v>11614285.845884666</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="19">
         <f>G6+G16</f>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" s="19">
         <f>G18</f>
@@ -10192,7 +10192,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C69" s="19">
         <f>G8+G20</f>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" s="78">
         <f>SUM(C66:C69)</f>
@@ -10215,19 +10215,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C72" s="209" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F72" s="223"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
@@ -10238,12 +10238,12 @@
         <v>-1686297.0770576668</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
@@ -10254,12 +10254,12 @@
         <v>8.8874494321901079</v>
       </c>
       <c r="F74" s="223" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="261"/>
       <c r="D75" s="262">
@@ -10267,12 +10267,12 @@
         <v>3372594.1541153337</v>
       </c>
       <c r="F75" s="223" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C76" s="230"/>
       <c r="D76" s="248">
@@ -10280,7 +10280,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="223" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10288,19 +10288,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D78" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F78" s="223"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="19">
         <f>G7+G17</f>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C80" s="19">
         <f>G19</f>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="19">
         <f>G9+G21</f>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="78">
         <f>SUM(C79:C81)</f>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -10367,15 +10367,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="215" t="s">
         <v>242</v>
-      </c>
-      <c r="D85" s="215" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
@@ -10392,7 +10392,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
@@ -10409,7 +10409,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
@@ -10479,7 +10479,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="50"/>
       <c r="E1" s="50"/>
@@ -10532,12 +10532,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="53"/>
       <c r="E2" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="53"/>
       <c r="G2" s="35"/>
@@ -10555,7 +10555,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10565,7 +10565,7 @@
       <c r="E3" s="237"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10632,7 +10632,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="266">
         <f>C26</f>
@@ -10687,7 +10687,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="267">
         <f>C4+C5</f>
@@ -10742,7 +10742,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="266">
         <f>C35</f>
@@ -10797,7 +10797,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
@@ -10854,7 +10854,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C9" s="300">
         <f>C61</f>
@@ -10911,7 +10911,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="266">
         <f>C48</f>
@@ -10966,7 +10966,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
@@ -11021,7 +11021,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
@@ -11076,7 +11076,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="266">
         <f>-C4*C79</f>
@@ -11133,7 +11133,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
@@ -11190,7 +11190,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="266">
         <f>BS!$G$39*BS!D58</f>
@@ -11245,7 +11245,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
@@ -11300,7 +11300,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="266">
         <f>-C4*C83</f>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="236" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="272"/>
@@ -11326,14 +11326,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="266">
         <v>0</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="273"/>
@@ -11351,7 +11351,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
@@ -11427,12 +11427,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="53"/>
       <c r="E21" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="35"/>
@@ -11450,7 +11450,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="26"/>
@@ -11471,7 +11471,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="274">
         <f>-C4*C29</f>
@@ -11528,7 +11528,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="266">
         <f>-C4*C30</f>
@@ -11585,7 +11585,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="266">
         <f>-C4*C31</f>
@@ -11642,7 +11642,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="267">
         <f>SUM(C23:C25)</f>
@@ -11703,14 +11703,14 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" s="237"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="60">
         <f>G29</f>
@@ -11882,7 +11882,7 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
@@ -11941,14 +11941,14 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" s="237"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C35" s="276">
         <f>G35</f>
@@ -12009,14 +12009,14 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="237"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12075,21 +12075,21 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E40" s="237"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="457">
         <v>0.25</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12143,12 +12143,12 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="53"/>
       <c r="E43" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="35"/>
@@ -12166,14 +12166,14 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="237"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="266">
         <f>-BS!G31*Normalized_FCF!C52</f>
@@ -12228,7 +12228,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
@@ -12283,7 +12283,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" s="278">
         <f>BS!$C$66*C51</f>
@@ -12340,7 +12340,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
@@ -12399,17 +12399,17 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E50" s="237"/>
       <c r="G50" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="84">
         <v>6.0000000000000001E-3</v>
@@ -12433,7 +12433,7 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="79">
         <v>0.06</v>
@@ -12457,7 +12457,7 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
@@ -12516,17 +12516,17 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="237"/>
       <c r="G55" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="266">
         <f>BS!$C67*C64</f>
@@ -12581,7 +12581,7 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" s="266">
         <f>BS!$C68*C65</f>
@@ -12636,7 +12636,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="266">
         <f>BS!$C69*C66</f>
@@ -12691,7 +12691,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="267">
         <f>SUM(C56:C58)</f>
@@ -12746,13 +12746,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="279">
         <v>0</v>
       </c>
       <c r="E60" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="266">
         <f>Data!C58</f>
@@ -12802,7 +12802,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61" s="267">
         <f>C59+C60</f>
@@ -12861,17 +12861,17 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="237"/>
       <c r="G63" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="158">
         <f>G64</f>
@@ -12896,7 +12896,7 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="158">
         <f>G65</f>
@@ -12921,7 +12921,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="158">
         <f>G66</f>
@@ -12946,7 +12946,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C67" s="68">
         <f>C59/BS!C70</f>
@@ -12976,12 +12976,12 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="51"/>
       <c r="D69" s="53"/>
       <c r="E69" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="35"/>
@@ -12999,7 +12999,7 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C70" s="59"/>
       <c r="D70" s="26"/>
@@ -13020,7 +13020,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
@@ -13077,7 +13077,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
@@ -13134,7 +13134,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
@@ -13191,7 +13191,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
@@ -13248,7 +13248,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C75" s="74">
         <f t="shared" si="22"/>
@@ -13305,7 +13305,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
@@ -13362,7 +13362,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
@@ -13419,7 +13419,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
@@ -13534,7 +13534,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
@@ -13591,7 +13591,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
@@ -13648,7 +13648,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -13707,7 +13707,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" s="233">
         <v>0</v>
@@ -13733,7 +13733,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" s="74">
         <v>0</v>
@@ -13757,7 +13757,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
@@ -13818,7 +13818,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" s="237"/>
     </row>
@@ -13937,7 +13937,7 @@
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
@@ -13992,7 +13992,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C91" s="292">
         <v>0</v>
@@ -14013,20 +14013,20 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5066079295154186E-2</v>
+        <v>3.3800424628450107E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5066079295154186E-2</v>
+        <v>3.3800424628450107E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.6674008810572683E-2</v>
+        <v>5.4628450106157106E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14072,7 +14072,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="26"/>
@@ -14093,7 +14093,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C95" s="74">
         <f>C4/G4-1</f>
@@ -14150,7 +14150,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
@@ -14210,12 +14210,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="51"/>
       <c r="D98" s="53"/>
       <c r="E98" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F98" s="53"/>
       <c r="G98" s="35"/>
@@ -14233,11 +14233,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="237"/>
       <c r="G99" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
@@ -14300,7 +14300,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="281">
         <f>BS!C4</f>
@@ -14357,7 +14357,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C102" s="281">
         <f>BS!C6+BS!C7</f>
@@ -14414,7 +14414,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C103" s="280">
         <f>BS!G30</f>
@@ -14471,7 +14471,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="280">
         <f>BS!G27</f>
@@ -14532,14 +14532,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C106" s="25"/>
       <c r="D106" s="25"/>
       <c r="E106" s="238"/>
       <c r="F106" s="25"/>
       <c r="G106" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -14555,7 +14555,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107" s="91">
         <f>C101/C$4</f>
@@ -14612,7 +14612,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C108" s="91">
         <f>C102/C$4</f>
@@ -14669,7 +14669,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C109" s="91">
         <f>BS!$G$38/C$4</f>
@@ -14700,18 +14700,18 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E111" s="237"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -14761,7 +14761,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C113" s="151"/>
       <c r="E113" s="459">
@@ -14820,10 +14820,10 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" s="451" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
@@ -14879,7 +14879,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C116" s="22">
         <f>C77</f>
@@ -14936,7 +14936,7 @@
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C117" s="452">
         <f>G117</f>
@@ -14993,7 +14993,7 @@
     </row>
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C118" s="15">
         <f>C100/C104</f>
@@ -15053,7 +15053,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
@@ -15132,12 +15132,12 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C121" s="51"/>
       <c r="D121" s="53"/>
       <c r="E121" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="53"/>
       <c r="G121" s="35"/>
@@ -15155,7 +15155,7 @@
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C122" s="161"/>
       <c r="D122" s="26"/>
@@ -15234,22 +15234,22 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8327751401365794E-2</v>
+        <v>6.5861569291337727E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6758166128637553E-2</v>
+        <v>6.4348635716351271E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2301748790537889E-2</v>
+        <v>6.0053065713172406E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15290,16 +15290,16 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.077519516274094E-2</v>
+        <v>7.7859742258777898E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4332535372216221E-2</v>
+        <v>7.1649620082773174E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16052,7 +16052,7 @@
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -16067,22 +16067,22 @@
     </row>
     <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
@@ -16093,7 +16093,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F4" s="275">
         <f>-BS!G31</f>
@@ -16104,7 +16104,7 @@
         <v>HKD</v>
       </c>
       <c r="H4" s="308" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I4" s="305">
         <f>Normalized_FCF!C4</f>
@@ -16114,14 +16114,14 @@
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="188">
         <f>Equity_Cost</f>
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
@@ -16132,7 +16132,7 @@
         <v>HKD</v>
       </c>
       <c r="H5" s="308" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I5" s="305">
         <f>Normalized_FCF!C7</f>
@@ -16142,7 +16142,7 @@
     </row>
     <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -16153,7 +16153,7 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F6" s="284">
         <f>BS!H42</f>
@@ -16164,7 +16164,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="308" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
@@ -16175,14 +16175,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C7" s="275">
         <f>F7</f>
         <v>6924831.8458846658</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
@@ -16193,7 +16193,7 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="312" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I7" s="313">
         <f>Normalized_FCF!C9</f>
@@ -16205,7 +16205,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
@@ -16216,7 +16216,7 @@
         <v>HKD</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16266,7 +16266,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
@@ -16277,7 +16277,7 @@
         <v>HKD</v>
       </c>
       <c r="H10" s="308" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I10" s="306">
         <f>Normalized_FCF!C41</f>
@@ -16288,7 +16288,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16304,7 +16304,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16319,25 +16319,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C14" s="309" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16352,7 +16352,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16362,14 +16362,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
         <v>3.4071209167200502E-2</v>
       </c>
       <c r="E16" s="308" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
@@ -16378,40 +16378,40 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
         <v>0.20764453215246692</v>
       </c>
       <c r="E17" s="308" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
         <v>0.20764453215246689</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="308" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
         <v>0</v>
       </c>
       <c r="H18" s="140" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -16427,41 +16427,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B20" s="121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D20" s="121" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>528</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>551</v>
+      </c>
+      <c r="K20" s="121" t="s">
         <v>529</v>
       </c>
-      <c r="J20" s="121" t="s">
-        <v>552</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>530</v>
-      </c>
       <c r="L20" s="122" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18016,7 +18016,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
@@ -18064,10 +18064,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="460" t="s">
-        <v>420</v>
-      </c>
-      <c r="K52" s="460"/>
+      <c r="J52" s="468" t="s">
+        <v>419</v>
+      </c>
+      <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>71328036.646042943</v>
@@ -18078,7 +18078,7 @@
     </row>
     <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="128"/>
       <c r="D54" s="128"/>
@@ -18547,7 +18547,7 @@
     </row>
     <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="275"/>
       <c r="D71" s="111"/>
@@ -19071,19 +19071,19 @@
     </row>
     <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" s="153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D89" s="153" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="154" t="s">
         <v>99</v>
       </c>
-      <c r="E89" s="154" t="s">
-        <v>100</v>
-      </c>
       <c r="F89" s="154" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G89" s="323"/>
       <c r="H89" s="323"/>
@@ -19351,7 +19351,7 @@
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -19361,16 +19361,16 @@
     </row>
     <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E3" s="97"/>
     </row>
     <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="449">
         <v>2</v>
@@ -19398,7 +19398,7 @@
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="446" t="str">
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
@@ -19411,7 +19411,7 @@
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" s="447">
         <f>Normalized_FCF!G8</f>
@@ -19424,7 +19424,7 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
@@ -19437,7 +19437,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
@@ -19457,7 +19457,7 @@
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C11" s="448"/>
       <c r="D11" s="469"/>
@@ -19467,7 +19467,7 @@
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="249" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19480,7 +19480,7 @@
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="249" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19493,7 +19493,7 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="249" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19506,7 +19506,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19516,21 +19516,21 @@
     </row>
     <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="137">
         <v>15</v>
       </c>
       <c r="E18" s="450" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F18" s="319"/>
     </row>
@@ -19540,35 +19540,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C22" s="324">
         <v>0.05</v>
@@ -19592,7 +19592,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C23" s="324">
         <v>0.03</v>
@@ -19615,7 +19615,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C24" s="324">
         <v>0.01</v>
@@ -19638,7 +19638,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19652,33 +19652,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C29" s="324">
         <v>0.06</v>
@@ -19701,7 +19701,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C30" s="324">
         <v>0</v>
@@ -19728,12 +19728,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19744,7 +19744,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19753,27 +19753,27 @@
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16555583542529126</v>
+        <v>0.15094880681171671</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
@@ -19784,7 +19784,7 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19793,7 +19793,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19804,15 +19804,15 @@
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F36" s="331" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19826,24 +19826,24 @@
         <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
         <v>0.20764453215246689</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
@@ -19853,7 +19853,7 @@
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -19863,15 +19863,15 @@
     </row>
     <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E44" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C45" s="150">
         <f>C18</f>
@@ -19879,24 +19879,24 @@
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="138">
         <v>3.4071209167200502E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
@@ -19907,24 +19907,24 @@
         <v>HKD</v>
       </c>
       <c r="E47" s="221" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E49" s="222" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
@@ -19934,19 +19934,19 @@
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E51" s="221" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C52" s="218" t="str">
         <f>IF(C46&gt;8%,"Y","N")</f>
@@ -19956,14 +19956,14 @@
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
@@ -19972,7 +19972,7 @@
     </row>
     <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="35"/>
       <c r="D55" s="35"/>
@@ -19982,12 +19982,12 @@
     </row>
     <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C57" s="219">
         <f>Holding_Period</f>
@@ -19997,7 +19997,7 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C58" s="155">
         <f>C33</f>
@@ -20010,34 +20010,34 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E60" s="413"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C61" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D61" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E61" s="154" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
@@ -20062,7 +20062,7 @@
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
@@ -20087,28 +20087,28 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C65" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D65" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E65" s="154" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
@@ -20133,7 +20133,7 @@
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
@@ -20183,7 +20183,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B2" s="345"/>
       <c r="C2" s="345"/>
@@ -20197,7 +20197,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
@@ -20206,7 +20206,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C4" s="423" t="str">
         <f>Thesis!C4</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="D4" s="349"/>
       <c r="E4" s="434" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F4" s="437" t="str">
         <f>Thesis!F4</f>
@@ -20223,14 +20223,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C5" s="355" t="str">
         <f>Thesis!C5</f>
         <v>0151.HK</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F5" s="439" t="str">
         <f>Thesis!F5</f>
@@ -20239,7 +20239,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C6" s="352" t="str">
         <f>Thesis!C6</f>
@@ -20249,7 +20249,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C7" s="352" t="str">
         <f>Market_currency</f>
@@ -20260,16 +20260,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
@@ -20278,18 +20278,18 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>53585.942952900004</v>
+        <v>55592.465045849996</v>
       </c>
       <c r="D10" s="343" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16555583542529126</v>
+        <v>0.15094880681171671</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,31 +20297,31 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
-        <v>497</v>
-      </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="B12" s="474" t="s">
+        <v>496</v>
+      </c>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C15" s="358" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="351" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E15" s="344" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20330,14 +20330,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C16" s="358" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="351" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
@@ -20346,14 +20346,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
         <v>0.02</v>
       </c>
       <c r="D17" s="351" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E17" s="344" t="str">
         <f>Reporting_currency</f>
@@ -20370,7 +20370,7 @@
         <v>6.6277455556474951</v>
       </c>
       <c r="D18" s="350" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E18" s="426">
         <f>Thesis!E18</f>
@@ -20379,14 +20379,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="343" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20399,14 +20399,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C21" s="361" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="362" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E21" s="363">
         <f>Holding_Period</f>
@@ -20415,14 +20415,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
         <v>3.3058505032532972</v>
       </c>
       <c r="D22" s="365" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
@@ -20431,14 +20431,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
         <v>4.170852752110819</v>
       </c>
       <c r="D23" s="365" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
@@ -20447,14 +20447,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
         <v>5.1345919269174427</v>
       </c>
       <c r="D24" s="365" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E24" s="368">
         <f>Thesis!E24</f>
@@ -20463,14 +20463,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
         <v>5.7883592149489207</v>
       </c>
       <c r="D25" s="365" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E25" s="368">
         <f>Thesis!E25</f>
@@ -20479,7 +20479,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B27" s="345"/>
       <c r="C27" s="345"/>
@@ -20488,26 +20488,26 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
+        <v>497</v>
+      </c>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="477" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
-        <v>499</v>
-      </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C32" s="370">
         <f>scaling_factor</f>
@@ -20516,7 +20516,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C33" s="470"/>
       <c r="D33" s="470"/>
@@ -20525,7 +20525,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="373">
         <f>Normalized_FCF!C8</f>
@@ -20542,7 +20542,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C36" s="470"/>
       <c r="D36" s="470"/>
@@ -20551,7 +20551,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="373">
         <f>Normalized_FCF!C15</f>
@@ -20564,7 +20564,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
@@ -20577,7 +20577,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C40" s="470"/>
       <c r="D40" s="470"/>
@@ -20586,7 +20586,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="373">
         <f>Normalized_FCF!C9</f>
@@ -20599,7 +20599,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C43" s="470"/>
       <c r="D43" s="470"/>
@@ -20608,7 +20608,7 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
@@ -20623,7 +20623,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="376">
         <f>Normalized_FCF!C45</f>
@@ -20638,7 +20638,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
@@ -20651,12 +20651,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="373">
         <f>Normalized_FCF!C13</f>
@@ -20669,7 +20669,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C51" s="470"/>
       <c r="D51" s="470"/>
@@ -20678,7 +20678,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
@@ -20691,16 +20691,16 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
-        <v>506</v>
-      </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+        <v>505</v>
+      </c>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="373">
         <f>Normalized_FCF!C17</f>
@@ -20712,26 +20712,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
+        <v>506</v>
+      </c>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
-        <v>508</v>
-      </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
@@ -20744,7 +20744,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
@@ -20757,24 +20757,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8327751401365794E-2</v>
+        <v>6.5861569291337727E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5066079295154186E-2</v>
+        <v>3.3800424628450107E-2</v>
       </c>
       <c r="E63" s="372" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
@@ -20783,18 +20783,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C65" s="381" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D65" s="381" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
@@ -20849,7 +20849,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B71" s="345"/>
       <c r="C71" s="345"/>
@@ -20862,40 +20862,40 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
-        <v>509</v>
-      </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="B73" s="474" t="s">
+        <v>508</v>
+      </c>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
-        <v>479</v>
-      </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="B74" s="477" t="s">
+        <v>478</v>
+      </c>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
-        <v>510</v>
-      </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="B77" s="474" t="s">
+        <v>509</v>
+      </c>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="373">
         <f>DCF!F4</f>
@@ -20908,7 +20908,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -20921,7 +20921,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="388">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -20930,7 +20930,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C81" s="389">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -20939,12 +20939,12 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
@@ -20957,7 +20957,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C85" s="390">
         <f>BS!C66</f>
@@ -20970,7 +20970,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -20983,12 +20983,12 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="373">
         <f>DCF!F6</f>
@@ -21001,7 +21001,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -21014,7 +21014,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
@@ -21027,7 +21027,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B94" s="345"/>
       <c r="C94" s="345"/>
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
-        <v>513</v>
-      </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="B96" s="474" t="s">
+        <v>512</v>
+      </c>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
-        <v>514</v>
-      </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="B97" s="477" t="s">
+        <v>513</v>
+      </c>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
-        <v>515</v>
-      </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="B98" s="477" t="s">
+        <v>514</v>
+      </c>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21074,13 +21074,13 @@
     <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C101" s="368">
         <f>E25+C103</f>
@@ -21090,7 +21090,7 @@
     <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C102" s="383">
         <f>E25</f>
@@ -21100,7 +21100,7 @@
     <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C103" s="383">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -21110,7 +21110,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C104" s="368">
         <v>0</v>
@@ -21123,29 +21123,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C106" s="392"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
-        <v>516</v>
-      </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="B107" s="474" t="s">
+        <v>515</v>
+      </c>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
-        <v>535</v>
-      </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="B108" s="474" t="s">
+        <v>534</v>
+      </c>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21153,13 +21153,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
@@ -21173,7 +21173,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
-        <v>517</v>
-      </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="B114" s="474" t="s">
+        <v>516</v>
+      </c>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21203,25 +21203,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C117" s="342" t="s">
         <v>378</v>
       </c>
-      <c r="C117" s="342" t="s">
+      <c r="D117" s="342" t="s">
+        <v>98</v>
+      </c>
+      <c r="E117" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="D117" s="342" t="s">
-        <v>99</v>
-      </c>
-      <c r="E117" s="342" t="s">
+      <c r="F117" s="342" t="s">
         <v>380</v>
-      </c>
-      <c r="F117" s="342" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21338,7 +21338,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C124" s="470"/>
       <c r="D124" s="470"/>
@@ -21347,7 +21347,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
@@ -21359,17 +21359,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
-        <v>519</v>
-      </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="B127" s="472" t="s">
+        <v>518</v>
+      </c>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B129" s="345"/>
       <c r="C129" s="345"/>
@@ -21378,31 +21378,31 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
+        <v>519</v>
+      </c>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
-        <v>521</v>
-      </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C135" s="405">
         <f>E21</f>
@@ -21411,7 +21411,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
@@ -21424,33 +21424,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
@@ -21471,7 +21471,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
@@ -21492,26 +21492,26 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
@@ -21532,7 +21532,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
@@ -21553,7 +21553,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B147" s="345"/>
       <c r="C147" s="345"/>
@@ -21562,51 +21562,51 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
-        <v>522</v>
-      </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="B149" s="475" t="s">
+        <v>521</v>
+      </c>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
-        <v>523</v>
-      </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="B152" s="476" t="s">
+        <v>522</v>
+      </c>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C158" s="470"/>
       <c r="D158" s="470"/>
@@ -21615,58 +21615,55 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
+        <v>387</v>
+      </c>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
-        <v>389</v>
-      </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520F7135-C9D5-48E5-A778-53BFF3EF1BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB837868-28E5-4267-99F2-6C1D8B66249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55592.465045849996</v>
+        <v>55002.3114891</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15094880681171671</v>
+        <v>0.15516968304016918</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.5861569291337727E-2</v>
+        <v>6.6568238489742637E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3800424628450107E-2</v>
+        <v>3.4163090128755368E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3800424628450107E-2</v>
+        <v>3.4163090128755368E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3800424628450107E-2</v>
+        <v>3.4163090128755368E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4628450106157106E-2</v>
+        <v>5.5214592274678106E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5861569291337727E-2</v>
+        <v>6.6568238489742637E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4348635716351271E-2</v>
+        <v>6.5039071721891523E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0053065713172406E-2</v>
+        <v>6.0697411911811591E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7859742258777898E-2</v>
+        <v>7.8695147218636019E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1649620082773174E-2</v>
+        <v>7.2418392830442421E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15094880681171671</v>
+        <v>0.15516968304016918</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55592.465045849996</v>
+        <v>55002.3114891</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15094880681171671</v>
+        <v>0.15516968304016918</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.5861569291337727E-2</v>
+        <v>6.6568238489742637E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3800424628450107E-2</v>
+        <v>3.4163090128755368E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB837868-28E5-4267-99F2-6C1D8B66249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FE92D9-64CE-4AAB-ACB2-CFDBA0906B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>55002.3114891</v>
+        <v>53113.820107500003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15516968304016918</v>
+        <v>0.16910116369269609</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6568238489742637E-2</v>
+        <v>6.8935109191600161E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4163090128755368E-2</v>
+        <v>3.5377777777777779E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4163090128755368E-2</v>
+        <v>3.5377777777777779E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4163090128755368E-2</v>
+        <v>3.5377777777777779E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5214592274678106E-2</v>
+        <v>5.7177777777777772E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6568238489742637E-2</v>
+        <v>6.8935109191600161E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5039071721891523E-2</v>
+        <v>6.7351572049780997E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.0697411911811591E-2</v>
+        <v>6.2855542113120444E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8695147218636019E-2</v>
+        <v>8.1493196897520853E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2418392830442421E-2</v>
+        <v>7.4993269019969264E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15516968304016918</v>
+        <v>0.16910116369269609</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>55002.3114891</v>
+        <v>53113.820107500003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15516968304016918</v>
+        <v>0.16910116369269609</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6568238489742637E-2</v>
+        <v>6.8935109191600161E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4163090128755368E-2</v>
+        <v>3.5377777777777779E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FE92D9-64CE-4AAB-ACB2-CFDBA0906B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0F06CB-E8F2-4334-A259-496CAB2E3A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>53113.820107500003</v>
+        <v>52995.789396150001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16910116369269609</v>
+        <v>0.16999419596707349</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8935109191600161E-2</v>
+        <v>6.9088639501603724E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5377777777777779E-2</v>
+        <v>3.5456570155902006E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5377777777777779E-2</v>
+        <v>3.5456570155902006E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5377777777777779E-2</v>
+        <v>3.5456570155902006E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7177777777777772E-2</v>
+        <v>5.7305122494432065E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8935109191600161E-2</v>
+        <v>6.9088639501603724E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7351572049780997E-2</v>
+        <v>6.7501575551005458E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2855542113120444E-2</v>
+        <v>6.2995532184641878E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1493196897520853E-2</v>
+        <v>8.1674696222459653E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4993269019969264E-2</v>
+        <v>7.5160291890837783E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16910116369269609</v>
+        <v>0.16999419596707349</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>53113.820107500003</v>
+        <v>52995.789396150001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16910116369269609</v>
+        <v>0.16999419596707349</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8935109191600161E-2</v>
+        <v>6.9088639501603724E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5377777777777779E-2</v>
+        <v>3.5456570155902006E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0F06CB-E8F2-4334-A259-496CAB2E3A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2B2F56-6D86-4779-89AD-297AA9BD8394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.49</v>
+        <v>4.63</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>52995.789396150001</v>
+        <v>54648.219355049994</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16999419596707349</v>
+        <v>0.15773186966665081</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9088639501603724E-2</v>
+        <v>6.6999566168941843E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5456570155902006E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5456570155902006E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5456570155902006E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7305122494432065E-2</v>
+        <v>5.5572354211663059E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9088639501603724E-2</v>
+        <v>6.6999566168941843E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7501575551005458E-2</v>
+        <v>6.5460491193091691E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2995532184641878E-2</v>
+        <v>6.1090699677978838E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1674696222459653E-2</v>
+        <v>7.9205050980311859E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5160291890837783E-2</v>
+        <v>7.2887626477291939E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.49</v>
+        <v>4.63</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16999419596707349</v>
+        <v>0.15773186966665081</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.49</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>52995.789396150001</v>
+        <v>54648.219355049994</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16999419596707349</v>
+        <v>0.15773186966665081</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9088639501603724E-2</v>
+        <v>6.6999566168941843E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5456570155902006E-2</v>
+        <v>3.4384449244060478E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2B2F56-6D86-4779-89AD-297AA9BD8394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7B57B7-CDBD-4748-868E-816C071EAFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>54648.219355049994</v>
+        <v>53940.035086950003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15773186966665081</v>
+        <v>0.16292458996433268</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6999566168941843E-2</v>
+        <v>6.7879210363720063E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4835886214442016E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4835886214442016E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4835886214442016E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5572354211663059E-2</v>
+        <v>5.6301969365426689E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6999566168941843E-2</v>
+        <v>6.7879210363720063E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5460491193091691E-2</v>
+        <v>6.6319928714226359E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.1090699677978838E-2</v>
+        <v>6.1892765756901974E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9205050980311859E-2</v>
+        <v>8.0244942240447231E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2887626477291939E-2</v>
+        <v>7.384457562141393E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15773186966665081</v>
+        <v>0.16292458996433268</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>54648.219355049994</v>
+        <v>53940.035086950003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15773186966665081</v>
+        <v>0.16292458996433268</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6999566168941843E-2</v>
+        <v>6.7879210363720063E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4384449244060478E-2</v>
+        <v>3.4835886214442016E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7B57B7-CDBD-4748-868E-816C071EAFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB68A2-3C41-47BA-B527-CC7B200B0339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>53940.035086950003</v>
+        <v>52641.697262099995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16292458996433268</v>
+        <v>0.17268960085927029</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7879210363720063E-2</v>
+        <v>6.9553361291973259E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4835886214442016E-2</v>
+        <v>3.5695067264573992E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4835886214442016E-2</v>
+        <v>3.5695067264573992E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4835886214442016E-2</v>
+        <v>3.5695067264573992E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.6301969365426689E-2</v>
+        <v>5.7690582959641253E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7879210363720063E-2</v>
+        <v>6.9553361291973259E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6319928714226359E-2</v>
+        <v>6.7955622023321643E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.1892765756901974E-2</v>
+        <v>6.3419268948215701E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0244942240447231E-2</v>
+        <v>8.2224077587184724E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.384457562141393E-2</v>
+        <v>7.5665854392345661E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16292458996433268</v>
+        <v>0.17268960085927029</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>53940.035086950003</v>
+        <v>52641.697262099995</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16292458996433268</v>
+        <v>0.17268960085927029</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7879210363720063E-2</v>
+        <v>6.9553361291973259E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4835886214442016E-2</v>
+        <v>3.5695067264573992E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB68A2-3C41-47BA-B527-CC7B200B0339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDB25B6-6F08-42A5-8FA9-C35FF2BFF9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,12 +21658,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21678,15 +21681,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0151.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0151.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDB25B6-6F08-42A5-8FA9-C35FF2BFF9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43EB69B-FB14-4CD2-94DE-1A4D61A06D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>52641.697262099995</v>
+        <v>53231.850818849998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17268960085927029</v>
+        <v>0.1682108255912047</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9553361291973259E-2</v>
+        <v>6.8782259725543402E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5695067264573992E-2</v>
+        <v>3.5299334811529935E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14017,16 +14017,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5695067264573992E-2</v>
+        <v>3.5299334811529935E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5695067264573992E-2</v>
+        <v>3.5299334811529935E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7690582959641253E-2</v>
+        <v>5.7050997782705094E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15238,18 +15238,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9553361291973259E-2</v>
+        <v>6.8782259725543402E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7955622023321643E-2</v>
+        <v>6.7202233752553103E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.3419268948215701E-2</v>
+        <v>6.2716172840142359E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15295,11 +15295,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2224077587184724E-2</v>
+        <v>8.1312502447637228E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5665854392345661E-2</v>
+        <v>7.4826986827020325E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17268960085927029</v>
+        <v>0.1682108255912047</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20282,14 +20282,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>52641.697262099995</v>
+        <v>53231.850818849998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17268960085927029</v>
+        <v>0.1682108255912047</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20297,13 +20297,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20488,22 +20488,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20693,10 +20693,10 @@
       <c r="B54" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20712,22 +20712,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9553361291973259E-2</v>
+        <v>6.8782259725543402E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20771,7 +20771,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.5695067264573992E-2</v>
+        <v>3.5299334811529935E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20862,22 +20862,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20885,13 +20885,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21040,33 +21040,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>512</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21129,23 +21129,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>534</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,13 +21189,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21359,13 +21359,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21378,22 +21378,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>520</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21562,13 +21562,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21576,13 +21576,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>522</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21619,22 +21619,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21658,15 +21658,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21681,12 +21678,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
